--- a/src/resultados_partidos.xlsx
+++ b/src/resultados_partidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="371">
   <si>
     <t>id</t>
   </si>
@@ -88,6 +88,9 @@
     <t>hora_peru</t>
   </si>
   <si>
+    <t>fecha_peru_key</t>
+  </si>
+  <si>
     <t>Tipo de Resultado</t>
   </si>
   <si>
@@ -124,7 +127,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>2026-06-11T19:00:00.000Z</t>
+    <t>11/06/2026</t>
   </si>
   <si>
     <t>scheduled</t>
@@ -133,7 +136,10 @@
     <t>11 de junio</t>
   </si>
   <si>
-    <t>14:00</t>
+    <t>'14:00</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
   </si>
   <si>
     <t>Regular</t>
@@ -163,10 +169,10 @@
     <t>Guadalajara</t>
   </si>
   <si>
-    <t>2026-06-12T02:00:00.000Z</t>
-  </si>
-  <si>
-    <t>21:00</t>
+    <t>12/06/2026</t>
+  </si>
+  <si>
+    <t>'21:00</t>
   </si>
   <si>
     <t>Corea del Sur vs Chequia</t>
@@ -196,12 +202,12 @@
     <t>Canada</t>
   </si>
   <si>
-    <t>2026-06-12T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>12 de junio</t>
   </si>
   <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
     <t>Canadá vs Bosnia y Herzegovina</t>
   </si>
   <si>
@@ -226,10 +232,10 @@
     <t>Inglewood, CA</t>
   </si>
   <si>
-    <t>2026-06-13T01:00:00.000Z</t>
-  </si>
-  <si>
-    <t>20:00</t>
+    <t>13/06/2026</t>
+  </si>
+  <si>
+    <t>'20:00</t>
   </si>
   <si>
     <t>Estados Unidos vs Paraguay</t>
@@ -253,12 +259,12 @@
     <t>Santa Clara, CA</t>
   </si>
   <si>
-    <t>2026-06-13T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>13 de junio</t>
   </si>
   <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
     <t>Catar vs Suiza</t>
   </si>
   <si>
@@ -283,10 +289,7 @@
     <t>East Rutherford, NJ</t>
   </si>
   <si>
-    <t>2026-06-13T22:00:00.000Z</t>
-  </si>
-  <si>
-    <t>17:00</t>
+    <t>'17:00</t>
   </si>
   <si>
     <t>Brasil vs Marruecos</t>
@@ -310,7 +313,7 @@
     <t>Foxborough, MA</t>
   </si>
   <si>
-    <t>2026-06-14T01:00:00.000Z</t>
+    <t>14/06/2026</t>
   </si>
   <si>
     <t>Haití vs Escocia</t>
@@ -334,10 +337,7 @@
     <t>Vancouver, BC</t>
   </si>
   <si>
-    <t>2026-06-14T04:00:00.000Z</t>
-  </si>
-  <si>
-    <t>23:00</t>
+    <t>'23:00</t>
   </si>
   <si>
     <t>Australia vs Turquía</t>
@@ -364,13 +364,13 @@
     <t>Houston, TX</t>
   </si>
   <si>
-    <t>2026-06-14T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>14 de junio</t>
   </si>
   <si>
-    <t>12:00</t>
+    <t>'12:00</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
   <si>
     <t>Alemania vs Curazao</t>
@@ -397,10 +397,7 @@
     <t>Arlington, TX</t>
   </si>
   <si>
-    <t>2026-06-14T20:00:00.000Z</t>
-  </si>
-  <si>
-    <t>15:00</t>
+    <t>'15:00</t>
   </si>
   <si>
     <t>Países Bajos vs Japón</t>
@@ -424,10 +421,7 @@
     <t>Philadelphia, PA</t>
   </si>
   <si>
-    <t>2026-06-14T23:00:00.000Z</t>
-  </si>
-  <si>
-    <t>18:00</t>
+    <t>'18:00</t>
   </si>
   <si>
     <t>Costa de Marfil vs Ecuador</t>
@@ -451,7 +445,7 @@
     <t>Monterrey</t>
   </si>
   <si>
-    <t>2026-06-15T02:00:00.000Z</t>
+    <t>15/06/2026</t>
   </si>
   <si>
     <t>Suecia vs Túnez</t>
@@ -478,13 +472,13 @@
     <t>Atlanta, GA</t>
   </si>
   <si>
-    <t>2026-06-15T16:00:00.000Z</t>
-  </si>
-  <si>
     <t>15 de junio</t>
   </si>
   <si>
-    <t>11:00</t>
+    <t>'11:00</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>España vs Cabo Verde</t>
@@ -511,9 +505,6 @@
     <t>Seattle, WA</t>
   </si>
   <si>
-    <t>2026-06-15T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>Bélgica vs Egipto</t>
   </si>
   <si>
@@ -535,9 +526,6 @@
     <t>Miami Gardens, FL</t>
   </si>
   <si>
-    <t>2026-06-15T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Arabia Saudita vs Uruguay</t>
   </si>
   <si>
@@ -553,7 +541,7 @@
     <t>NZL</t>
   </si>
   <si>
-    <t>2026-06-16T01:00:00.000Z</t>
+    <t>16/06/2026</t>
   </si>
   <si>
     <t>Irán vs Nueva Zelanda</t>
@@ -574,12 +562,12 @@
     <t>SEN</t>
   </si>
   <si>
-    <t>2026-06-16T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>16 de junio</t>
   </si>
   <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
     <t>Francia vs Senegal</t>
   </si>
   <si>
@@ -595,9 +583,6 @@
     <t>NOR</t>
   </si>
   <si>
-    <t>2026-06-16T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Irak vs Noruega</t>
   </si>
   <si>
@@ -622,7 +607,7 @@
     <t>Kansas City, MO</t>
   </si>
   <si>
-    <t>2026-06-17T01:00:00.000Z</t>
+    <t>17/06/2026</t>
   </si>
   <si>
     <t>Argentina vs Argelia</t>
@@ -640,9 +625,6 @@
     <t>JOR</t>
   </si>
   <si>
-    <t>2026-06-17T04:00:00.000Z</t>
-  </si>
-  <si>
     <t>Austria vs Jordania</t>
   </si>
   <si>
@@ -655,19 +637,19 @@
     <t>POR</t>
   </si>
   <si>
-    <t>República Democrática del Congo</t>
+    <t>RD del Congo</t>
   </si>
   <si>
     <t>COD</t>
   </si>
   <si>
-    <t>2026-06-17T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>17 de junio</t>
   </si>
   <si>
-    <t>Portugal vs República Democrática del Congo</t>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>Portugal vs RD del Congo</t>
   </si>
   <si>
     <t>L</t>
@@ -685,9 +667,6 @@
     <t>CRO</t>
   </si>
   <si>
-    <t>2026-06-17T20:00:00.000Z</t>
-  </si>
-  <si>
     <t>Inglaterra vs Croacia</t>
   </si>
   <si>
@@ -703,9 +682,6 @@
     <t>PAN</t>
   </si>
   <si>
-    <t>2026-06-17T23:00:00.000Z</t>
-  </si>
-  <si>
     <t>Ghana vs Panamá</t>
   </si>
   <si>
@@ -721,205 +697,166 @@
     <t>COL</t>
   </si>
   <si>
-    <t>2026-06-18T02:00:00.000Z</t>
+    <t>18/06/2026</t>
   </si>
   <si>
     <t>Uzbekistán vs Colombia</t>
   </si>
   <si>
-    <t>2026-06-18T16:00:00.000Z</t>
-  </si>
-  <si>
     <t>18 de junio</t>
   </si>
   <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
     <t>Chequia vs Sudáfrica</t>
   </si>
   <si>
-    <t>2026-06-18T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>Suiza vs Bosnia y Herzegovina</t>
   </si>
   <si>
-    <t>2026-06-18T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Canadá vs Catar</t>
   </si>
   <si>
-    <t>2026-06-19T01:00:00.000Z</t>
+    <t>19/06/2026</t>
   </si>
   <si>
     <t>México vs Corea del Sur</t>
   </si>
   <si>
-    <t>2026-06-19T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>19 de junio</t>
   </si>
   <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
     <t>Estados Unidos vs Australia</t>
   </si>
   <si>
-    <t>2026-06-19T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Escocia vs Marruecos</t>
   </si>
   <si>
-    <t>2026-06-20T01:00:00.000Z</t>
+    <t>20/06/2026</t>
   </si>
   <si>
     <t>Brasil vs Haití</t>
   </si>
   <si>
-    <t>2026-06-20T04:00:00.000Z</t>
-  </si>
-  <si>
     <t>Turquía vs Paraguay</t>
   </si>
   <si>
-    <t>2026-06-20T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>20 de junio</t>
   </si>
   <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
     <t>Países Bajos vs Suecia</t>
   </si>
   <si>
-    <t>2026-06-20T20:00:00.000Z</t>
-  </si>
-  <si>
     <t>Alemania vs Costa de Marfil</t>
   </si>
   <si>
-    <t>2026-06-21T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>19:00</t>
+    <t>21/06/2026</t>
+  </si>
+  <si>
+    <t>'19:00</t>
   </si>
   <si>
     <t>Ecuador vs Curazao</t>
   </si>
   <si>
-    <t>2026-06-21T04:00:00.000Z</t>
-  </si>
-  <si>
     <t>Túnez vs Japón</t>
   </si>
   <si>
-    <t>2026-06-21T16:00:00.000Z</t>
-  </si>
-  <si>
     <t>21 de junio</t>
   </si>
   <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
     <t>España vs Arabia Saudita</t>
   </si>
   <si>
-    <t>2026-06-21T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>Bélgica vs Irán</t>
   </si>
   <si>
-    <t>2026-06-21T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Uruguay vs Cabo Verde</t>
   </si>
   <si>
-    <t>2026-06-22T01:00:00.000Z</t>
+    <t>22/06/2026</t>
   </si>
   <si>
     <t>Nueva Zelanda vs Egipto</t>
   </si>
   <si>
-    <t>2026-06-22T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>22 de junio</t>
   </si>
   <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
     <t>Argentina vs Austria</t>
   </si>
   <si>
-    <t>2026-06-22T21:00:00.000Z</t>
-  </si>
-  <si>
-    <t>16:00</t>
+    <t>'16:00</t>
   </si>
   <si>
     <t>Francia vs Irak</t>
   </si>
   <si>
-    <t>2026-06-23T00:00:00.000Z</t>
+    <t>23/06/2026</t>
   </si>
   <si>
     <t>Noruega vs Senegal</t>
   </si>
   <si>
-    <t>2026-06-23T03:00:00.000Z</t>
-  </si>
-  <si>
-    <t>22:00</t>
+    <t>'22:00</t>
   </si>
   <si>
     <t>Jordania vs Argelia</t>
   </si>
   <si>
-    <t>2026-06-23T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>23 de junio</t>
   </si>
   <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
     <t>Portugal vs Uzbekistán</t>
   </si>
   <si>
-    <t>2026-06-23T20:00:00.000Z</t>
-  </si>
-  <si>
     <t>Inglaterra vs Ghana</t>
   </si>
   <si>
-    <t>2026-06-23T23:00:00.000Z</t>
-  </si>
-  <si>
     <t>Panamá vs Croacia</t>
   </si>
   <si>
-    <t>2026-06-24T02:00:00.000Z</t>
-  </si>
-  <si>
-    <t>Colombia vs República Democrática del Congo</t>
-  </si>
-  <si>
-    <t>2026-06-24T19:00:00.000Z</t>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>Colombia vs RD del Congo</t>
   </si>
   <si>
     <t>24 de junio</t>
   </si>
   <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
     <t>Bosnia y Herzegovina vs Catar</t>
   </si>
   <si>
     <t>Suiza vs Canadá</t>
   </si>
   <si>
-    <t>2026-06-24T22:00:00.000Z</t>
-  </si>
-  <si>
     <t>Escocia vs Brasil</t>
   </si>
   <si>
     <t>Marruecos vs Haití</t>
   </si>
   <si>
-    <t>2026-06-25T01:00:00.000Z</t>
+    <t>25/06/2026</t>
   </si>
   <si>
     <t>Chequia vs México</t>
@@ -928,28 +865,25 @@
     <t>Sudáfrica vs Corea del Sur</t>
   </si>
   <si>
-    <t>2026-06-25T20:00:00.000Z</t>
-  </si>
-  <si>
     <t>25 de junio</t>
   </si>
   <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
     <t>Curazao vs Costa de Marfil</t>
   </si>
   <si>
     <t>Ecuador vs Alemania</t>
   </si>
   <si>
-    <t>2026-06-25T23:00:00.000Z</t>
-  </si>
-  <si>
     <t>Túnez vs Países Bajos</t>
   </si>
   <si>
     <t>Japón vs Suecia</t>
   </si>
   <si>
-    <t>2026-06-26T02:00:00.000Z</t>
+    <t>26/06/2026</t>
   </si>
   <si>
     <t>Turquía vs Estados Unidos</t>
@@ -958,19 +892,19 @@
     <t>Paraguay vs Australia</t>
   </si>
   <si>
-    <t>2026-06-26T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>26 de junio</t>
   </si>
   <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
     <t>Senegal vs Irak</t>
   </si>
   <si>
     <t>Noruega vs Francia</t>
   </si>
   <si>
-    <t>2026-06-27T00:00:00.000Z</t>
+    <t>27/06/2026</t>
   </si>
   <si>
     <t>Cabo Verde vs Arabia Saudita</t>
@@ -979,40 +913,34 @@
     <t>Uruguay vs España</t>
   </si>
   <si>
-    <t>2026-06-27T03:00:00.000Z</t>
-  </si>
-  <si>
     <t>Egipto vs Irán</t>
   </si>
   <si>
     <t>Nueva Zelanda vs Bélgica</t>
   </si>
   <si>
-    <t>2026-06-27T21:00:00.000Z</t>
-  </si>
-  <si>
     <t>27 de junio</t>
   </si>
   <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
     <t>Panamá vs Inglaterra</t>
   </si>
   <si>
     <t>Croacia vs Ghana</t>
   </si>
   <si>
-    <t>2026-06-27T23:30:00.000Z</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>República Democrática del Congo vs Uzbekistán</t>
+    <t>'18:30</t>
+  </si>
+  <si>
+    <t>RD del Congo vs Uzbekistán</t>
   </si>
   <si>
     <t>Colombia vs Portugal</t>
   </si>
   <si>
-    <t>2026-06-28T02:00:00.000Z</t>
+    <t>28/06/2026</t>
   </si>
   <si>
     <t>Argelia vs Austria</t>
@@ -1024,175 +952,181 @@
     <t>R32</t>
   </si>
   <si>
-    <t>2026-06-28T19:00:00.000Z</t>
-  </si>
-  <si>
     <t>28 de junio</t>
   </si>
   <si>
-    <t>2026-06-29T17:00:00.000Z</t>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>29/06/2026</t>
   </si>
   <si>
     <t>29 de junio</t>
   </si>
   <si>
-    <t>2026-06-29T20:30:00.000Z</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>2026-06-30T01:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-06-30T17:00:00.000Z</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>'15:30</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
   </si>
   <si>
     <t>30 de junio</t>
   </si>
   <si>
-    <t>2026-06-30T21:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-01T01:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-01T16:00:00.000Z</t>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
   </si>
   <si>
     <t>1 de julio</t>
   </si>
   <si>
-    <t>2026-07-01T20:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-02T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-02T19:00:00.000Z</t>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>02/07/2026</t>
   </si>
   <si>
     <t>2 de julio</t>
   </si>
   <si>
-    <t>2026-07-02T23:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-03T03:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-03T18:00:00.000Z</t>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
   </si>
   <si>
     <t>3 de julio</t>
   </si>
   <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>2026-07-03T22:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-04T01:30:00.000Z</t>
-  </si>
-  <si>
-    <t>20:30</t>
+    <t>'13:00</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>04/07/2026</t>
+  </si>
+  <si>
+    <t>'20:30</t>
   </si>
   <si>
     <t>R16</t>
   </si>
   <si>
-    <t>2026-07-04T17:00:00.000Z</t>
-  </si>
-  <si>
     <t>4 de julio</t>
   </si>
   <si>
-    <t>2026-07-04T21:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-05T20:00:00.000Z</t>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>05/07/2026</t>
   </si>
   <si>
     <t>5 de julio</t>
   </si>
   <si>
-    <t>2026-07-06T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-06T19:00:00.000Z</t>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
   </si>
   <si>
     <t>6 de julio</t>
   </si>
   <si>
-    <t>2026-07-07T00:00:00.000Z</t>
-  </si>
-  <si>
-    <t>2026-07-07T16:00:00.000Z</t>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>07/07/2026</t>
   </si>
   <si>
     <t>7 de julio</t>
   </si>
   <si>
-    <t>2026-07-07T20:00:00.000Z</t>
+    <t>2026-07-07</t>
   </si>
   <si>
     <t>QF</t>
   </si>
   <si>
-    <t>2026-07-09T20:00:00.000Z</t>
+    <t>09/07/2026</t>
   </si>
   <si>
     <t>9 de julio</t>
   </si>
   <si>
-    <t>2026-07-10T19:00:00.000Z</t>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
   </si>
   <si>
     <t>10 de julio</t>
   </si>
   <si>
-    <t>2026-07-11T21:00:00.000Z</t>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>11/07/2026</t>
   </si>
   <si>
     <t>11 de julio</t>
   </si>
   <si>
-    <t>2026-07-12T01:00:00.000Z</t>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>12/07/2026</t>
   </si>
   <si>
     <t>SF</t>
   </si>
   <si>
-    <t>2026-07-14T19:00:00.000Z</t>
+    <t>14/07/2026</t>
   </si>
   <si>
     <t>14 de julio</t>
   </si>
   <si>
-    <t>2026-07-15T19:00:00.000Z</t>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
   </si>
   <si>
     <t>15 de julio</t>
   </si>
   <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
     <t>3rd</t>
   </si>
   <si>
-    <t>2026-07-18T21:00:00.000Z</t>
+    <t>18/07/2026</t>
   </si>
   <si>
     <t>18 de julio</t>
   </si>
   <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
     <t>final</t>
   </si>
   <si>
-    <t>2026-07-19T19:00:00.000Z</t>
+    <t>19/07/2026</t>
   </si>
   <si>
     <t>19 de julio</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
   </si>
 </sst>
 </file>
@@ -1254,9 +1188,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:AA105" totalsRowShown="0">
-  <autoFilter ref="A1:AA105"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:AB105" totalsRowShown="0">
+  <autoFilter ref="A1:AB105"/>
+  <tableColumns count="28">
     <tableColumn id="1" name="id" dataDxfId="0"/>
     <tableColumn id="2" name="match_number" dataDxfId="0"/>
     <tableColumn id="3" name="round" dataDxfId="1"/>
@@ -1281,9 +1215,10 @@
     <tableColumn id="22" name="status" dataDxfId="1"/>
     <tableColumn id="23" name="fecha_peru_str" dataDxfId="1"/>
     <tableColumn id="24" name="hora_peru" dataDxfId="1"/>
-    <tableColumn id="25" name="Tipo de Resultado" dataDxfId="1"/>
-    <tableColumn id="26" name="Ganador" dataDxfId="1"/>
-    <tableColumn id="27" name="Partido" dataDxfId="1"/>
+    <tableColumn id="25" name="fecha_peru_key" dataDxfId="1"/>
+    <tableColumn id="26" name="Tipo de Resultado" dataDxfId="1"/>
+    <tableColumn id="27" name="Ganador" dataDxfId="1"/>
+    <tableColumn id="28" name="Partido" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1574,10 +1509,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA105"/>
+  <dimension ref="A1:AB105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1659,8 +1594,11 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:27">
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -1668,70 +1606,73 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="1">
         <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="1">
         <v>14</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1739,70 +1680,73 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="1">
         <v>4</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="1">
         <v>16</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
       <c r="A4" s="1">
         <v>7</v>
       </c>
@@ -1810,70 +1754,73 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="1">
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="1">
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="A5" s="1">
         <v>20</v>
       </c>
@@ -1881,70 +1828,73 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="1">
         <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1">
         <v>3</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" s="1">
         <v>9</v>
       </c>
@@ -1952,70 +1902,73 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1">
         <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="1">
         <v>4</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" s="1">
         <v>13</v>
       </c>
@@ -2023,70 +1976,73 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1">
         <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="1">
         <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="1">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" s="1">
         <v>15</v>
       </c>
@@ -2094,70 +2050,73 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1">
         <v>11</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="1">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" s="1">
         <v>19</v>
       </c>
@@ -2165,70 +2124,73 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1">
         <v>16</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1">
         <v>12</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB9" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:28">
       <c r="A10" s="1">
         <v>26</v>
       </c>
@@ -2236,7 +2198,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>109</v>
@@ -2271,35 +2233,38 @@
         <v>115</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="X10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="Z10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:28">
       <c r="A11" s="1">
         <v>34</v>
       </c>
@@ -2307,7 +2272,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>120</v>
@@ -2342,35 +2307,38 @@
         <v>126</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="Y11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27">
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" s="1">
         <v>28</v>
       </c>
@@ -2378,7 +2346,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>109</v>
@@ -2387,61 +2355,64 @@
         <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="1">
         <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="1">
         <v>7</v>
       </c>
       <c r="N12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P12" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" s="1">
         <v>33</v>
       </c>
@@ -2449,7 +2420,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>120</v>
@@ -2458,61 +2429,64 @@
         <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="1">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="1">
         <v>15</v>
       </c>
       <c r="N13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" s="1">
         <v>43</v>
       </c>
@@ -2520,70 +2494,73 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E14" s="1">
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="1">
         <v>32</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="1">
         <v>17</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="X14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27">
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" s="1">
         <v>40</v>
       </c>
@@ -2591,70 +2568,73 @@
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" s="1">
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="1">
         <v>26</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="1">
         <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" s="1">
         <v>45</v>
       </c>
@@ -2662,70 +2642,73 @@
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E16" s="1">
         <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="1">
         <v>31</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="1">
         <v>5</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" s="1">
         <v>37</v>
       </c>
@@ -2733,70 +2716,73 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E17" s="1">
         <v>27</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="1">
         <v>28</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1">
         <v>3</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" s="1">
         <v>52</v>
       </c>
@@ -2804,70 +2790,73 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E18" s="1">
         <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="1">
         <v>34</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1">
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" s="1">
         <v>51</v>
       </c>
@@ -2875,70 +2864,73 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E19" s="1">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="1">
         <v>35</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="1">
         <v>9</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
       <c r="A20" s="1">
         <v>58</v>
       </c>
@@ -2946,70 +2938,73 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E20" s="1">
         <v>37</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="1">
         <v>38</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="1">
         <v>8</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28">
       <c r="A21" s="1">
         <v>55</v>
       </c>
@@ -3017,70 +3012,73 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E21" s="1">
         <v>39</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="1">
         <v>40</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="1">
         <v>4</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
       <c r="A22" s="1">
         <v>61</v>
       </c>
@@ -3088,29 +3086,29 @@
         <v>23</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E22" s="1">
         <v>41</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="1">
         <v>44</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="1">
@@ -3123,35 +3121,38 @@
         <v>115</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
       <c r="A23" s="1">
         <v>68</v>
       </c>
@@ -3159,29 +3160,29 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E23" s="1">
         <v>47</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="1">
         <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="1">
@@ -3194,35 +3195,38 @@
         <v>126</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
       <c r="A24" s="1">
         <v>70</v>
       </c>
@@ -3230,70 +3234,73 @@
         <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E24" s="1">
         <v>45</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="1">
         <v>46</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="1">
         <v>13</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
       <c r="A25" s="1">
         <v>63</v>
       </c>
@@ -3301,70 +3308,73 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E25" s="1">
         <v>42</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="1">
         <v>43</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="1">
         <v>14</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -3372,70 +3382,73 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="1">
         <v>3</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="1">
         <v>17</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB26" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28">
       <c r="A27" s="1">
         <v>8</v>
       </c>
@@ -3443,70 +3456,73 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E27" s="1">
         <v>7</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="1">
         <v>8</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="1">
         <v>3</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" s="1">
         <v>10</v>
       </c>
@@ -3514,70 +3530,73 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="1">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="1">
         <v>12</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -3585,70 +3604,73 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="1">
         <v>2</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="1">
         <v>16</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB29" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28">
       <c r="A30" s="1">
         <v>22</v>
       </c>
@@ -3656,70 +3678,73 @@
         <v>32</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E30" s="1">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="1">
         <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="1">
         <v>6</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" s="1">
         <v>14</v>
       </c>
@@ -3727,70 +3752,73 @@
         <v>30</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E31" s="1">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="1">
         <v>12</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="1">
         <v>9</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" s="1">
         <v>16</v>
       </c>
@@ -3798,70 +3826,73 @@
         <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E32" s="1">
         <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="1">
         <v>10</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="1">
         <v>7</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P32" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" s="1">
         <v>21</v>
       </c>
@@ -3869,70 +3900,73 @@
         <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E33" s="1">
         <v>16</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="1">
         <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="1">
         <v>4</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -3940,7 +3974,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>120</v>
@@ -3959,10 +3993,10 @@
         <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="1">
@@ -3975,35 +4009,38 @@
         <v>115</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28">
       <c r="A35" s="1">
         <v>29</v>
       </c>
@@ -4011,7 +4048,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>109</v>
@@ -4030,51 +4067,54 @@
         <v>17</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="1">
         <v>13</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB35" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28">
       <c r="A36" s="1">
         <v>25</v>
       </c>
@@ -4082,7 +4122,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>109</v>
@@ -4091,10 +4131,10 @@
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="1">
@@ -4111,41 +4151,44 @@
         <v>8</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB36" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4153,7 +4196,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>120</v>
@@ -4162,10 +4205,10 @@
         <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="1">
@@ -4182,41 +4225,44 @@
         <v>15</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="X37" s="2" t="s">
         <v>107</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB37" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28">
       <c r="A38" s="1">
         <v>47</v>
       </c>
@@ -4224,70 +4270,73 @@
         <v>38</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E38" s="1">
         <v>30</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="1">
         <v>29</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="1">
         <v>17</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA38" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4295,70 +4344,73 @@
         <v>39</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E39" s="1">
         <v>25</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="1">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="1">
         <v>3</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="Z39" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA39" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB39" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28">
       <c r="A40" s="1">
         <v>44</v>
       </c>
@@ -4366,70 +4418,73 @@
         <v>37</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E40" s="1">
         <v>31</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="1">
         <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="1">
         <v>5</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA40" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -4437,70 +4492,73 @@
         <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1">
         <v>28</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="1">
         <v>26</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="1">
         <v>12</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="Z41" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA41" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB41" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28">
       <c r="A42" s="1">
         <v>56</v>
       </c>
@@ -4508,29 +4566,29 @@
         <v>43</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E42" s="1">
         <v>37</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="1">
         <v>39</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="1">
@@ -4543,35 +4601,38 @@
         <v>126</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>40</v>
+        <v>259</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA42" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28">
       <c r="A43" s="1">
         <v>49</v>
       </c>
@@ -4579,70 +4640,73 @@
         <v>42</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E43" s="1">
         <v>33</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="1">
         <v>36</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O43" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O43" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P43" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>40</v>
+        <v>259</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA43" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB43" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28">
       <c r="A44" s="1">
         <v>53</v>
       </c>
@@ -4650,70 +4714,73 @@
         <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E44" s="1">
         <v>35</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="1">
         <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="1">
         <v>1</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>40</v>
+        <v>259</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA44" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" s="1">
         <v>59</v>
       </c>
@@ -4721,70 +4788,73 @@
         <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E45" s="1">
         <v>40</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="1">
         <v>38</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="1">
         <v>4</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>40</v>
+        <v>259</v>
       </c>
       <c r="Z45" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA45" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB45" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28">
       <c r="A46" s="1">
         <v>64</v>
       </c>
@@ -4792,29 +4862,29 @@
         <v>47</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E46" s="1">
         <v>41</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="1">
         <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="1">
@@ -4827,35 +4897,38 @@
         <v>115</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA46" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB46" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28">
       <c r="A47" s="1">
         <v>71</v>
       </c>
@@ -4863,70 +4936,73 @@
         <v>45</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E47" s="1">
         <v>47</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="1">
         <v>45</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="1">
         <v>9</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA47" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB47" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28">
       <c r="A48" s="1">
         <v>67</v>
       </c>
@@ -4934,70 +5010,73 @@
         <v>46</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E48" s="1">
         <v>46</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="1">
         <v>48</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="1">
         <v>13</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA48" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28">
       <c r="A49" s="1">
         <v>62</v>
       </c>
@@ -5005,70 +5084,73 @@
         <v>48</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E49" s="1">
         <v>43</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="1">
         <v>44</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="1">
         <v>16</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA49" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:28">
       <c r="A50" s="1">
         <v>11</v>
       </c>
@@ -5076,70 +5158,73 @@
         <v>52</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="1">
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="1">
         <v>6</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA50" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28">
       <c r="A51" s="1">
         <v>12</v>
       </c>
@@ -5147,70 +5232,73 @@
         <v>51</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E51" s="1">
         <v>7</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="1">
         <v>12</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA51" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28">
       <c r="A52" s="1">
         <v>18</v>
       </c>
@@ -5218,70 +5306,73 @@
         <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E52" s="1">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="1">
         <v>9</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="1">
         <v>5</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB52" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28">
       <c r="A53" s="1">
         <v>17</v>
       </c>
@@ -5289,70 +5380,73 @@
         <v>50</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E53" s="1">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="1">
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="1">
         <v>17</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA53" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB53" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -5360,70 +5454,73 @@
         <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E54" s="1">
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="1">
         <v>1</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="1">
         <v>14</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA54" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB54" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28">
       <c r="A55" s="1">
         <v>5</v>
       </c>
@@ -5431,70 +5528,73 @@
         <v>54</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E55" s="1">
         <v>3</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="1">
         <v>2</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="1">
         <v>15</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="Z55" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA55" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB55" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28">
       <c r="A56" s="1">
         <v>30</v>
       </c>
@@ -5502,7 +5602,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>109</v>
@@ -5521,51 +5621,54 @@
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="1">
         <v>7</v>
       </c>
       <c r="N56" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O56" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O56" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P56" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z56" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA56" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28">
       <c r="A57" s="1">
         <v>27</v>
       </c>
@@ -5573,7 +5676,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>109</v>
@@ -5582,10 +5685,10 @@
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="1">
@@ -5602,41 +5705,44 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z57" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA57" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28">
       <c r="A58" s="1">
         <v>36</v>
       </c>
@@ -5644,7 +5750,7 @@
         <v>58</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>120</v>
@@ -5653,10 +5759,10 @@
         <v>23</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="1">
@@ -5673,41 +5779,44 @@
         <v>8</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA58" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28">
       <c r="A59" s="1">
         <v>32</v>
       </c>
@@ -5715,7 +5824,7 @@
         <v>57</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>120</v>
@@ -5734,10 +5843,10 @@
         <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="1">
@@ -5750,35 +5859,38 @@
         <v>126</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z59" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA59" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB59" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28">
       <c r="A60" s="1">
         <v>24</v>
       </c>
@@ -5786,70 +5898,73 @@
         <v>59</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E60" s="1">
         <v>16</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="1">
         <v>13</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="1">
         <v>3</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z60" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA60" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB60" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28">
       <c r="A61" s="1">
         <v>23</v>
       </c>
@@ -5857,70 +5972,73 @@
         <v>60</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E61" s="1">
         <v>15</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="1">
         <v>14</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="1">
         <v>4</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y61" s="2" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="Z61" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA61" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB61" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28">
       <c r="A62" s="1">
         <v>50</v>
       </c>
@@ -5928,70 +6046,73 @@
         <v>62</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E62" s="1">
         <v>34</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="1">
         <v>36</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="1">
         <v>13</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z62" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA62" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28">
       <c r="A63" s="1">
         <v>54</v>
       </c>
@@ -5999,70 +6120,73 @@
         <v>61</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E63" s="1">
         <v>35</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="1">
         <v>33</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="1">
         <v>9</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z63" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA63" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28">
       <c r="A64" s="1">
         <v>48</v>
       </c>
@@ -6070,29 +6194,29 @@
         <v>65</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E64" s="1">
         <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="1">
         <v>29</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="1">
@@ -6105,35 +6229,38 @@
         <v>115</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z64" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA64" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB64" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28">
       <c r="A65" s="1">
         <v>46</v>
       </c>
@@ -6141,70 +6268,73 @@
         <v>66</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E65" s="1">
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="1">
         <v>30</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="1">
         <v>16</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z65" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA65" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB65" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28">
       <c r="A66" s="1">
         <v>39</v>
       </c>
@@ -6212,70 +6342,73 @@
         <v>63</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E66" s="1">
         <v>26</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="1">
         <v>27</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="1">
         <v>6</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
       <c r="V66" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA66" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB66" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28">
       <c r="A67" s="1">
         <v>42</v>
       </c>
@@ -6283,70 +6416,73 @@
         <v>64</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E67" s="1">
         <v>28</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="1">
         <v>25</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="1">
         <v>12</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
       <c r="V67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="Y67" s="2" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="Z67" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA67" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB67" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28">
       <c r="A68" s="1">
         <v>69</v>
       </c>
@@ -6354,70 +6490,73 @@
         <v>67</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E68" s="1">
         <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="1">
         <v>47</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="1">
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
       <c r="V68" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z68" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA68" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="69" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB68" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28">
       <c r="A69" s="1">
         <v>72</v>
       </c>
@@ -6425,70 +6564,73 @@
         <v>68</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E69" s="1">
         <v>48</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="1">
         <v>45</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="1">
         <v>7</v>
       </c>
       <c r="N69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O69" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P69" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
       <c r="V69" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y69" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z69" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA69" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB69" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28">
       <c r="A70" s="1">
         <v>65</v>
       </c>
@@ -6496,70 +6638,73 @@
         <v>72</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E70" s="1">
         <v>44</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="1">
         <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="1">
         <v>17</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z70" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA70" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="71" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28">
       <c r="A71" s="1">
         <v>66</v>
       </c>
@@ -6567,70 +6712,73 @@
         <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E71" s="1">
         <v>43</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="1">
         <v>41</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="1">
         <v>5</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
       <c r="V71" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="Y71" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z71" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA71" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB71" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28">
       <c r="A72" s="1">
         <v>57</v>
       </c>
@@ -6638,70 +6786,73 @@
         <v>69</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E72" s="1">
         <v>38</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="1">
         <v>39</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="1">
         <v>8</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
       <c r="V72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z72" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="73" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB72" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28">
       <c r="A73" s="1">
         <v>60</v>
       </c>
@@ -6709,29 +6860,29 @@
         <v>70</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E73" s="1">
         <v>40</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="1">
         <v>37</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="1">
@@ -6744,35 +6895,38 @@
         <v>126</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
       <c r="V73" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>40</v>
+        <v>302</v>
       </c>
       <c r="Z73" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA73" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27">
+        <v>43</v>
+      </c>
+      <c r="AB73" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28">
       <c r="A74" s="1">
         <v>82</v>
       </c>
@@ -6780,7 +6934,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="1"/>
@@ -6795,39 +6949,42 @@
         <v>3</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
       <c r="V74" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>40</v>
+        <v>313</v>
       </c>
       <c r="Z74" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA74" s="2"/>
-    </row>
-    <row r="75" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA74" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB74" s="2"/>
+    </row>
+    <row r="75" spans="1:28">
       <c r="A75" s="1">
         <v>95</v>
       </c>
@@ -6835,7 +6992,7 @@
         <v>76</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="1"/>
@@ -6856,33 +7013,36 @@
         <v>115</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
       <c r="V75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y75" s="2" t="s">
-        <v>40</v>
+        <v>316</v>
       </c>
       <c r="Z75" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA75" s="2"/>
-    </row>
-    <row r="76" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA75" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB75" s="2"/>
+    </row>
+    <row r="76" spans="1:28">
       <c r="A76" s="1">
         <v>93</v>
       </c>
@@ -6890,7 +7050,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="1"/>
@@ -6905,39 +7065,42 @@
         <v>9</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
       <c r="V76" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>40</v>
+        <v>316</v>
       </c>
       <c r="Z76" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA76" s="2"/>
-    </row>
-    <row r="77" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB76" s="2"/>
+    </row>
+    <row r="77" spans="1:28">
       <c r="A77" s="1">
         <v>101</v>
       </c>
@@ -6945,7 +7108,7 @@
         <v>75</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="1"/>
@@ -6960,39 +7123,42 @@
         <v>15</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
       <c r="V77" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>40</v>
+        <v>316</v>
       </c>
       <c r="Z77" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA77" s="2"/>
-    </row>
-    <row r="78" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB77" s="2"/>
+    </row>
+    <row r="78" spans="1:28">
       <c r="A78" s="1">
         <v>79</v>
       </c>
@@ -7000,7 +7166,7 @@
         <v>78</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="1"/>
@@ -7021,33 +7187,36 @@
         <v>126</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
       <c r="V78" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="Z78" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA78" s="2"/>
-    </row>
-    <row r="79" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB78" s="2"/>
+    </row>
+    <row r="79" spans="1:28">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -7055,7 +7224,7 @@
         <v>77</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="1"/>
@@ -7070,39 +7239,42 @@
         <v>1</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
       <c r="V79" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y79" s="2" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="Z79" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA79" s="2"/>
-    </row>
-    <row r="80" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB79" s="2"/>
+    </row>
+    <row r="80" spans="1:28">
       <c r="A80" s="1">
         <v>100</v>
       </c>
@@ -7110,7 +7282,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="1"/>
@@ -7125,39 +7297,42 @@
         <v>14</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
       <c r="V80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="Z80" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA80" s="2"/>
-    </row>
-    <row r="81" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB80" s="2"/>
+    </row>
+    <row r="81" spans="1:28">
       <c r="A81" s="1">
         <v>104</v>
       </c>
@@ -7165,7 +7340,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="1"/>
@@ -7180,39 +7355,42 @@
         <v>17</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
       <c r="V81" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y81" s="2" t="s">
-        <v>40</v>
+        <v>323</v>
       </c>
       <c r="Z81" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA81" s="2"/>
-    </row>
-    <row r="82" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB81" s="2"/>
+    </row>
+    <row r="82" spans="1:28">
       <c r="A82" s="1">
         <v>88</v>
       </c>
@@ -7220,7 +7398,7 @@
         <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="1"/>
@@ -7235,39 +7413,42 @@
         <v>6</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
       <c r="T82" s="2"/>
       <c r="U82" s="2"/>
       <c r="V82" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>40</v>
+        <v>323</v>
       </c>
       <c r="Z82" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA82" s="2"/>
-    </row>
-    <row r="83" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB82" s="2"/>
+    </row>
+    <row r="83" spans="1:28">
       <c r="A83" s="1">
         <v>83</v>
       </c>
@@ -7275,7 +7456,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="1"/>
@@ -7290,39 +7471,42 @@
         <v>4</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
       <c r="V83" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y83" s="2" t="s">
-        <v>40</v>
+        <v>323</v>
       </c>
       <c r="Z83" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA83" s="2"/>
-    </row>
-    <row r="84" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB83" s="2"/>
+    </row>
+    <row r="84" spans="1:28">
       <c r="A84" s="1">
         <v>81</v>
       </c>
@@ -7330,7 +7514,7 @@
         <v>84</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="1"/>
@@ -7345,39 +7529,42 @@
         <v>3</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
       <c r="V84" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="Z84" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA84" s="2"/>
-    </row>
-    <row r="85" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB84" s="2"/>
+    </row>
+    <row r="85" spans="1:28">
       <c r="A85" s="1">
         <v>98</v>
       </c>
@@ -7385,7 +7572,7 @@
         <v>83</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="1"/>
@@ -7400,39 +7587,42 @@
         <v>13</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
       <c r="V85" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="Z85" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA85" s="2"/>
-    </row>
-    <row r="86" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB85" s="2"/>
+    </row>
+    <row r="86" spans="1:28">
       <c r="A86" s="1">
         <v>97</v>
       </c>
@@ -7440,7 +7630,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="1"/>
@@ -7455,39 +7645,42 @@
         <v>12</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="Z86" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA86" s="2"/>
-    </row>
-    <row r="87" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB86" s="2"/>
+    </row>
+    <row r="87" spans="1:28">
       <c r="A87" s="1">
         <v>78</v>
       </c>
@@ -7495,7 +7688,7 @@
         <v>88</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="1"/>
@@ -7516,33 +7709,36 @@
         <v>126</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>355</v>
+        <v>327</v>
       </c>
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="Z87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA87" s="2"/>
-    </row>
-    <row r="88" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB87" s="2"/>
+    </row>
+    <row r="88" spans="1:28">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -7550,7 +7746,7 @@
         <v>86</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="1"/>
@@ -7565,39 +7761,42 @@
         <v>5</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="Z88" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA88" s="2"/>
-    </row>
-    <row r="89" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB88" s="2"/>
+    </row>
+    <row r="89" spans="1:28">
       <c r="A89" s="1">
         <v>91</v>
       </c>
@@ -7605,7 +7804,7 @@
         <v>87</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="1"/>
@@ -7620,39 +7819,42 @@
         <v>8</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="Z89" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA89" s="2"/>
-    </row>
-    <row r="90" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB89" s="2"/>
+    </row>
+    <row r="90" spans="1:28">
       <c r="A90" s="1">
         <v>94</v>
       </c>
@@ -7660,7 +7862,7 @@
         <v>90</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="1"/>
@@ -7681,33 +7883,36 @@
         <v>115</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>40</v>
+        <v>335</v>
       </c>
       <c r="Z90" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA90" s="2"/>
-    </row>
-    <row r="91" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB90" s="2"/>
+    </row>
+    <row r="91" spans="1:28">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -7715,7 +7920,7 @@
         <v>89</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="1"/>
@@ -7730,39 +7935,42 @@
         <v>7</v>
       </c>
       <c r="N91" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="O91" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="P91" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
       <c r="V91" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>40</v>
+        <v>335</v>
       </c>
       <c r="Z91" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA91" s="2"/>
-    </row>
-    <row r="92" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB91" s="2"/>
+    </row>
+    <row r="92" spans="1:28">
       <c r="A92" s="1">
         <v>74</v>
       </c>
@@ -7770,7 +7978,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="1"/>
@@ -7785,39 +7993,42 @@
         <v>1</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="Z92" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA92" s="2"/>
-    </row>
-    <row r="93" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB92" s="2"/>
+    </row>
+    <row r="93" spans="1:28">
       <c r="A93" s="1">
         <v>99</v>
       </c>
@@ -7825,7 +8036,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="1"/>
@@ -7840,39 +8051,42 @@
         <v>14</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
       <c r="V93" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="Z93" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA93" s="2"/>
-    </row>
-    <row r="94" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA93" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB93" s="2"/>
+    </row>
+    <row r="94" spans="1:28">
       <c r="A94" s="1">
         <v>77</v>
       </c>
@@ -7880,7 +8094,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="1"/>
@@ -7901,33 +8115,36 @@
         <v>126</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
       <c r="V94" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="Z94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA94" s="2"/>
-    </row>
-    <row r="95" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB94" s="2"/>
+    </row>
+    <row r="95" spans="1:28">
       <c r="A95" s="1">
         <v>87</v>
       </c>
@@ -7935,7 +8152,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="1"/>
@@ -7950,39 +8167,42 @@
         <v>6</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
       <c r="V95" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="Z95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA95" s="2"/>
-    </row>
-    <row r="96" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB95" s="2"/>
+    </row>
+    <row r="96" spans="1:28">
       <c r="A96" s="1">
         <v>103</v>
       </c>
@@ -7990,7 +8210,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="1"/>
@@ -8005,39 +8225,42 @@
         <v>17</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
       <c r="V96" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="Z96" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA96" s="2"/>
-    </row>
-    <row r="97" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA96" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB96" s="2"/>
+    </row>
+    <row r="97" spans="1:28">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -8045,7 +8268,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="1"/>
@@ -8060,39 +8283,42 @@
         <v>12</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>373</v>
+        <v>342</v>
       </c>
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
       <c r="V97" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>40</v>
+        <v>344</v>
       </c>
       <c r="Z97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA97" s="2"/>
-    </row>
-    <row r="98" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB97" s="2"/>
+    </row>
+    <row r="98" spans="1:28">
       <c r="A98" s="1">
         <v>92</v>
       </c>
@@ -8100,7 +8326,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="1"/>
@@ -8115,39 +8341,42 @@
         <v>9</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
       <c r="V98" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>40</v>
+        <v>348</v>
       </c>
       <c r="Z98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA98" s="2"/>
-    </row>
-    <row r="99" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB98" s="2"/>
+    </row>
+    <row r="99" spans="1:28">
       <c r="A99" s="1">
         <v>80</v>
       </c>
@@ -8155,7 +8384,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="1"/>
@@ -8170,39 +8399,42 @@
         <v>3</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
       <c r="V99" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>40</v>
+        <v>351</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA99" s="2"/>
-    </row>
-    <row r="100" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB99" s="2"/>
+    </row>
+    <row r="100" spans="1:28">
       <c r="A100" s="1">
         <v>85</v>
       </c>
@@ -8210,7 +8442,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="1"/>
@@ -8225,39 +8457,42 @@
         <v>5</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
       <c r="V100" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>40</v>
+        <v>354</v>
       </c>
       <c r="Z100" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA100" s="2"/>
-    </row>
-    <row r="101" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB100" s="2"/>
+    </row>
+    <row r="101" spans="1:28">
       <c r="A101" s="1">
         <v>90</v>
       </c>
@@ -8265,7 +8500,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="1"/>
@@ -8280,39 +8515,42 @@
         <v>8</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
       <c r="V101" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>40</v>
+        <v>354</v>
       </c>
       <c r="Z101" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA101" s="2"/>
-    </row>
-    <row r="102" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB101" s="2"/>
+    </row>
+    <row r="102" spans="1:28">
       <c r="A102" s="1">
         <v>76</v>
       </c>
@@ -8320,7 +8558,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="1"/>
@@ -8341,33 +8579,36 @@
         <v>126</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
       <c r="V102" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>40</v>
+        <v>359</v>
       </c>
       <c r="Z102" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA102" s="2"/>
-    </row>
-    <row r="103" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB102" s="2"/>
+    </row>
+    <row r="103" spans="1:28">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -8375,7 +8616,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="1"/>
@@ -8390,39 +8631,42 @@
         <v>17</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
       <c r="V103" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>40</v>
+        <v>362</v>
       </c>
       <c r="Z103" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA103" s="2"/>
-    </row>
-    <row r="104" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB103" s="2"/>
+    </row>
+    <row r="104" spans="1:28">
       <c r="A104" s="1">
         <v>84</v>
       </c>
@@ -8430,7 +8674,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="1"/>
@@ -8445,39 +8689,42 @@
         <v>5</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
       <c r="V104" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>40</v>
+        <v>366</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA104" s="2"/>
-    </row>
-    <row r="105" spans="1:27">
+        <v>42</v>
+      </c>
+      <c r="AA104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB104" s="2"/>
+    </row>
+    <row r="105" spans="1:28">
       <c r="A105" s="1">
         <v>73</v>
       </c>
@@ -8485,7 +8732,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="1"/>
@@ -8500,37 +8747,40 @@
         <v>1</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
       <c r="V105" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>40</v>
+        <v>370</v>
       </c>
       <c r="Z105" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA105" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="AA105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB105" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/resultados_partidos.xlsx
+++ b/src/resultados_partidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="372">
   <si>
     <t>id</t>
   </si>
@@ -130,46 +130,49 @@
     <t>11/06/2026</t>
   </si>
   <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>11 de junio</t>
+  </si>
+  <si>
+    <t>'14:00</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Por jugar</t>
+  </si>
+  <si>
+    <t>México vs Sudáfrica</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>Chequia</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>Estadio Akron</t>
+  </si>
+  <si>
+    <t>Guadalajara</t>
+  </si>
+  <si>
+    <t>12/06/2026</t>
+  </si>
+  <si>
     <t>scheduled</t>
-  </si>
-  <si>
-    <t>11 de junio</t>
-  </si>
-  <si>
-    <t>'14:00</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Por jugar</t>
-  </si>
-  <si>
-    <t>México vs Sudáfrica</t>
-  </si>
-  <si>
-    <t>Corea del Sur</t>
-  </si>
-  <si>
-    <t>KOR</t>
-  </si>
-  <si>
-    <t>Chequia</t>
-  </si>
-  <si>
-    <t>CZE</t>
-  </si>
-  <si>
-    <t>Estadio Akron</t>
-  </si>
-  <si>
-    <t>Guadalajara</t>
-  </si>
-  <si>
-    <t>12/06/2026</t>
   </si>
   <si>
     <t>'21:00</t>
@@ -1208,8 +1211,8 @@
     <tableColumn id="15" name="stadium_city" dataDxfId="1"/>
     <tableColumn id="16" name="stadium_country" dataDxfId="1"/>
     <tableColumn id="17" name="kickoff_utc" dataDxfId="1"/>
-    <tableColumn id="18" name="home_score" dataDxfId="1"/>
-    <tableColumn id="19" name="away_score" dataDxfId="1"/>
+    <tableColumn id="18" name="home_score" dataDxfId="0"/>
+    <tableColumn id="19" name="away_score" dataDxfId="0"/>
     <tableColumn id="20" name="home_pen" dataDxfId="1"/>
     <tableColumn id="21" name="away_pen" dataDxfId="1"/>
     <tableColumn id="22" name="status" dataDxfId="1"/>
@@ -1646,8 +1649,12 @@
       <c r="Q2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2" t="s">
@@ -1720,18 +1727,18 @@
       <c r="Q3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="2" t="s">
         <v>41</v>
@@ -1743,7 +1750,7 @@
         <v>43</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -1757,58 +1764,58 @@
         <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="1">
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="1">
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z4" s="2" t="s">
         <v>42</v>
@@ -1817,7 +1824,7 @@
         <v>43</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -1831,58 +1838,58 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="1">
         <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1">
         <v>3</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>42</v>
@@ -1891,7 +1898,7 @@
         <v>43</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -1905,58 +1912,58 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1">
         <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="1">
         <v>4</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>42</v>
@@ -1965,7 +1972,7 @@
         <v>43</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -1979,58 +1986,58 @@
         <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1">
         <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="1">
         <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="1">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>42</v>
@@ -2039,7 +2046,7 @@
         <v>43</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -2053,58 +2060,58 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1">
         <v>11</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="1">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z8" s="2" t="s">
         <v>42</v>
@@ -2113,7 +2120,7 @@
         <v>43</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -2127,58 +2134,58 @@
         <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="1">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1">
         <v>16</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1">
         <v>12</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z9" s="2" t="s">
         <v>42</v>
@@ -2187,7 +2194,7 @@
         <v>43</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -2201,58 +2208,58 @@
         <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" s="1">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1">
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="1">
         <v>10</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z10" s="2" t="s">
         <v>42</v>
@@ -2261,7 +2268,7 @@
         <v>43</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2275,58 +2282,58 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" s="1">
         <v>21</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="1">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="1">
         <v>2</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z11" s="2" t="s">
         <v>42</v>
@@ -2335,7 +2342,7 @@
         <v>43</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -2349,58 +2356,58 @@
         <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E12" s="1">
         <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="1">
         <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="1">
         <v>7</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>42</v>
@@ -2409,7 +2416,7 @@
         <v>43</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -2423,58 +2430,58 @@
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1">
         <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="1">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="1">
         <v>15</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z13" s="2" t="s">
         <v>42</v>
@@ -2483,7 +2490,7 @@
         <v>43</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -2497,58 +2504,58 @@
         <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E14" s="1">
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="1">
         <v>32</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="1">
         <v>17</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z14" s="2" t="s">
         <v>42</v>
@@ -2557,7 +2564,7 @@
         <v>43</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -2571,58 +2578,58 @@
         <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1">
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="1">
         <v>26</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="1">
         <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>42</v>
@@ -2631,7 +2638,7 @@
         <v>43</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -2645,58 +2652,58 @@
         <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" s="1">
         <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="1">
         <v>31</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="1">
         <v>5</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z16" s="2" t="s">
         <v>42</v>
@@ -2705,7 +2712,7 @@
         <v>43</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:28">
@@ -2719,58 +2726,58 @@
         <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E17" s="1">
         <v>27</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="1">
         <v>28</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1">
         <v>3</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>42</v>
@@ -2779,7 +2786,7 @@
         <v>43</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -2793,58 +2800,58 @@
         <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E18" s="1">
         <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="1">
         <v>34</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1">
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>42</v>
@@ -2853,7 +2860,7 @@
         <v>43</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -2867,58 +2874,58 @@
         <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E19" s="1">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="1">
         <v>35</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="1">
         <v>9</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>42</v>
@@ -2927,7 +2934,7 @@
         <v>43</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:28">
@@ -2941,58 +2948,58 @@
         <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="1">
         <v>37</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="1">
         <v>38</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="1">
         <v>8</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>42</v>
@@ -3001,7 +3008,7 @@
         <v>43</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -3015,58 +3022,58 @@
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" s="1">
         <v>39</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="1">
         <v>40</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="1">
         <v>4</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z21" s="2" t="s">
         <v>42</v>
@@ -3075,7 +3082,7 @@
         <v>43</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -3089,58 +3096,58 @@
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E22" s="1">
         <v>41</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="1">
         <v>44</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="1">
         <v>10</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>42</v>
@@ -3149,7 +3156,7 @@
         <v>43</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:28">
@@ -3163,58 +3170,58 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E23" s="1">
         <v>47</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="1">
         <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="1">
         <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>42</v>
@@ -3223,7 +3230,7 @@
         <v>43</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -3237,58 +3244,58 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E24" s="1">
         <v>45</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="1">
         <v>46</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="1">
         <v>13</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>42</v>
@@ -3297,7 +3304,7 @@
         <v>43</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -3311,26 +3318,26 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E25" s="1">
         <v>42</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="1">
         <v>43</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="1">
@@ -3346,23 +3353,23 @@
         <v>36</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>42</v>
@@ -3371,7 +3378,7 @@
         <v>43</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:28">
@@ -3411,32 +3418,32 @@
         <v>17</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z26" s="2" t="s">
         <v>42</v>
@@ -3445,7 +3452,7 @@
         <v>43</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:28">
@@ -3459,58 +3466,58 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1">
         <v>7</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="1">
         <v>8</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="1">
         <v>3</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="X27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y27" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z27" s="2" t="s">
         <v>42</v>
@@ -3519,7 +3526,7 @@
         <v>43</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -3533,58 +3540,58 @@
         <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="1">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="1">
         <v>12</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>42</v>
@@ -3593,7 +3600,7 @@
         <v>43</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:28">
@@ -3642,23 +3649,23 @@
         <v>36</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>42</v>
@@ -3667,7 +3674,7 @@
         <v>43</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:28">
@@ -3681,58 +3688,58 @@
         <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" s="1">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="1">
         <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="1">
         <v>6</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z30" s="2" t="s">
         <v>42</v>
@@ -3741,7 +3748,7 @@
         <v>43</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -3755,58 +3762,58 @@
         <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31" s="1">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="1">
         <v>12</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="1">
         <v>9</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z31" s="2" t="s">
         <v>42</v>
@@ -3815,7 +3822,7 @@
         <v>43</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:28">
@@ -3829,58 +3836,58 @@
         <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="1">
         <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="1">
         <v>10</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="1">
         <v>7</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>42</v>
@@ -3889,7 +3896,7 @@
         <v>43</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -3903,58 +3910,58 @@
         <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E33" s="1">
         <v>16</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="1">
         <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="1">
         <v>4</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>42</v>
@@ -3963,7 +3970,7 @@
         <v>43</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -3977,58 +3984,58 @@
         <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E34" s="1">
         <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="1">
         <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="1">
         <v>10</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>42</v>
@@ -4037,7 +4044,7 @@
         <v>43</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -4051,58 +4058,58 @@
         <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" s="1">
         <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="1">
         <v>17</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="1">
         <v>13</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>42</v>
@@ -4111,7 +4118,7 @@
         <v>43</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:28">
@@ -4125,58 +4132,58 @@
         <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E36" s="1">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="1">
         <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="1">
         <v>8</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
       <c r="V36" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>42</v>
@@ -4185,7 +4192,7 @@
         <v>43</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:28">
@@ -4199,58 +4206,58 @@
         <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E37" s="1">
         <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="1">
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="1">
         <v>15</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
       <c r="V37" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>42</v>
@@ -4259,7 +4266,7 @@
         <v>43</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:28">
@@ -4273,58 +4280,58 @@
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E38" s="1">
         <v>30</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="1">
         <v>29</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="1">
         <v>17</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>42</v>
@@ -4333,7 +4340,7 @@
         <v>43</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -4347,58 +4354,58 @@
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E39" s="1">
         <v>25</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="1">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="1">
         <v>3</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
       <c r="V39" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>42</v>
@@ -4407,7 +4414,7 @@
         <v>43</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:28">
@@ -4421,58 +4428,58 @@
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" s="1">
         <v>31</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="1">
         <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="1">
         <v>5</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="R40" s="2"/>
-      <c r="S40" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>42</v>
@@ -4481,7 +4488,7 @@
         <v>43</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:28">
@@ -4495,58 +4502,58 @@
         <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E41" s="1">
         <v>28</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="1">
         <v>26</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="1">
         <v>12</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
       <c r="V41" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z41" s="2" t="s">
         <v>42</v>
@@ -4555,7 +4562,7 @@
         <v>43</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:28">
@@ -4569,58 +4576,58 @@
         <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E42" s="1">
         <v>37</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="1">
         <v>39</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="1">
         <v>2</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
       <c r="V42" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z42" s="2" t="s">
         <v>42</v>
@@ -4629,7 +4636,7 @@
         <v>43</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:28">
@@ -4643,58 +4650,58 @@
         <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E43" s="1">
         <v>33</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="1">
         <v>36</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="R43" s="2"/>
-      <c r="S43" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>42</v>
@@ -4703,7 +4710,7 @@
         <v>43</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:28">
@@ -4717,58 +4724,58 @@
         <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E44" s="1">
         <v>35</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="1">
         <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="1">
         <v>1</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R44" s="2"/>
-      <c r="S44" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
       <c r="V44" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>42</v>
@@ -4777,7 +4784,7 @@
         <v>43</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" spans="1:28">
@@ -4791,58 +4798,58 @@
         <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E45" s="1">
         <v>40</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="1">
         <v>38</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="1">
         <v>4</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R45" s="2"/>
-      <c r="S45" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
       <c r="V45" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>42</v>
@@ -4851,7 +4858,7 @@
         <v>43</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:28">
@@ -4865,58 +4872,58 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E46" s="1">
         <v>41</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="1">
         <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="1">
         <v>10</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
       <c r="V46" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>42</v>
@@ -4925,7 +4932,7 @@
         <v>43</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:28">
@@ -4939,58 +4946,58 @@
         <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E47" s="1">
         <v>47</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="1">
         <v>45</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="1">
         <v>9</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>42</v>
@@ -4999,7 +5006,7 @@
         <v>43</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="48" spans="1:28">
@@ -5013,58 +5020,58 @@
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E48" s="1">
         <v>46</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="1">
         <v>48</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="1">
         <v>13</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>42</v>
@@ -5073,7 +5080,7 @@
         <v>43</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:28">
@@ -5087,26 +5094,26 @@
         <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E49" s="1">
         <v>43</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="1">
         <v>44</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="1">
@@ -5122,23 +5129,23 @@
         <v>36</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z49" s="2" t="s">
         <v>42</v>
@@ -5147,7 +5154,7 @@
         <v>43</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:28">
@@ -5161,58 +5168,58 @@
         <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="1">
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="1">
         <v>6</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
       <c r="V50" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z50" s="2" t="s">
         <v>42</v>
@@ -5221,7 +5228,7 @@
         <v>43</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:28">
@@ -5235,58 +5242,58 @@
         <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E51" s="1">
         <v>7</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="1">
         <v>12</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
       <c r="V51" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z51" s="2" t="s">
         <v>42</v>
@@ -5295,7 +5302,7 @@
         <v>43</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:28">
@@ -5309,58 +5316,58 @@
         <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="1">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="1">
         <v>9</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="1">
         <v>5</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
       <c r="V52" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z52" s="2" t="s">
         <v>42</v>
@@ -5369,7 +5376,7 @@
         <v>43</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:28">
@@ -5383,58 +5390,58 @@
         <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" s="1">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="1">
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="1">
         <v>17</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z53" s="2" t="s">
         <v>42</v>
@@ -5443,7 +5450,7 @@
         <v>43</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:28">
@@ -5492,23 +5499,23 @@
         <v>36</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R54" s="2"/>
-      <c r="S54" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>42</v>
@@ -5517,7 +5524,7 @@
         <v>43</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="55" spans="1:28">
@@ -5557,32 +5564,32 @@
         <v>15</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R55" s="2"/>
-      <c r="S55" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
       <c r="V55" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z55" s="2" t="s">
         <v>42</v>
@@ -5591,7 +5598,7 @@
         <v>43</v>
       </c>
       <c r="AB55" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:28">
@@ -5605,58 +5612,58 @@
         <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E56" s="1">
         <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="1">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="1">
         <v>7</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R56" s="2"/>
-      <c r="S56" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
       <c r="V56" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>42</v>
@@ -5665,7 +5672,7 @@
         <v>43</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:28">
@@ -5679,58 +5686,58 @@
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E57" s="1">
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="1">
         <v>19</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="1">
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
       <c r="V57" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z57" s="2" t="s">
         <v>42</v>
@@ -5739,7 +5746,7 @@
         <v>43</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:28">
@@ -5753,58 +5760,58 @@
         <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E58" s="1">
         <v>23</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="1">
         <v>21</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="1">
         <v>8</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
       <c r="V58" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>42</v>
@@ -5813,7 +5820,7 @@
         <v>43</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:28">
@@ -5827,58 +5834,58 @@
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E59" s="1">
         <v>22</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="1">
         <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="1">
         <v>2</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
       <c r="V59" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z59" s="2" t="s">
         <v>42</v>
@@ -5887,7 +5894,7 @@
         <v>43</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:28">
@@ -5901,58 +5908,58 @@
         <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E60" s="1">
         <v>16</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="1">
         <v>13</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="1">
         <v>3</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
       <c r="V60" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z60" s="2" t="s">
         <v>42</v>
@@ -5961,7 +5968,7 @@
         <v>43</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -5975,58 +5982,58 @@
         <v>28</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E61" s="1">
         <v>15</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="1">
         <v>14</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="1">
         <v>4</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
       <c r="V61" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y61" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z61" s="2" t="s">
         <v>42</v>
@@ -6035,7 +6042,7 @@
         <v>43</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -6049,58 +6056,58 @@
         <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E62" s="1">
         <v>34</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="1">
         <v>36</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="1">
         <v>13</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
       <c r="V62" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y62" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>42</v>
@@ -6109,7 +6116,7 @@
         <v>43</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -6123,58 +6130,58 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E63" s="1">
         <v>35</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="1">
         <v>33</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="1">
         <v>9</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
       <c r="V63" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z63" s="2" t="s">
         <v>42</v>
@@ -6183,7 +6190,7 @@
         <v>43</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -6197,58 +6204,58 @@
         <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E64" s="1">
         <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="1">
         <v>29</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="1">
         <v>10</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
       <c r="V64" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>42</v>
@@ -6257,7 +6264,7 @@
         <v>43</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="1:28">
@@ -6271,26 +6278,26 @@
         <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E65" s="1">
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="1">
         <v>30</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="1">
@@ -6306,23 +6313,23 @@
         <v>36</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
       <c r="V65" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z65" s="2" t="s">
         <v>42</v>
@@ -6331,7 +6338,7 @@
         <v>43</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:28">
@@ -6345,58 +6352,58 @@
         <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E66" s="1">
         <v>26</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="1">
         <v>27</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="1">
         <v>6</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
       <c r="V66" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>42</v>
@@ -6405,7 +6412,7 @@
         <v>43</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -6419,58 +6426,58 @@
         <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E67" s="1">
         <v>28</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="1">
         <v>25</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="1">
         <v>12</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
       <c r="V67" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Y67" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z67" s="2" t="s">
         <v>42</v>
@@ -6479,7 +6486,7 @@
         <v>43</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="1:28">
@@ -6493,58 +6500,58 @@
         <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E68" s="1">
         <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="1">
         <v>47</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="1">
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
       <c r="V68" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>42</v>
@@ -6553,7 +6560,7 @@
         <v>43</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="69" spans="1:28">
@@ -6567,58 +6574,58 @@
         <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E69" s="1">
         <v>48</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="1">
         <v>45</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="1">
         <v>7</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
       <c r="V69" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y69" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z69" s="2" t="s">
         <v>42</v>
@@ -6627,7 +6634,7 @@
         <v>43</v>
       </c>
       <c r="AB69" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -6641,58 +6648,58 @@
         <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E70" s="1">
         <v>44</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="1">
         <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="1">
         <v>17</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
       <c r="V70" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>42</v>
@@ -6701,7 +6708,7 @@
         <v>43</v>
       </c>
       <c r="AB70" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -6715,58 +6722,58 @@
         <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E71" s="1">
         <v>43</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="1">
         <v>41</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="1">
         <v>5</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
       <c r="V71" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Y71" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>42</v>
@@ -6775,7 +6782,7 @@
         <v>43</v>
       </c>
       <c r="AB71" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="72" spans="1:28">
@@ -6789,58 +6796,58 @@
         <v>28</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E72" s="1">
         <v>38</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="1">
         <v>39</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="1">
         <v>8</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
       <c r="V72" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>42</v>
@@ -6849,7 +6856,7 @@
         <v>43</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -6863,58 +6870,58 @@
         <v>28</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E73" s="1">
         <v>40</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="1">
         <v>37</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="1">
         <v>2</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
       <c r="V73" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z73" s="2" t="s">
         <v>42</v>
@@ -6923,7 +6930,7 @@
         <v>43</v>
       </c>
       <c r="AB73" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:28">
@@ -6934,7 +6941,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="1"/>
@@ -6949,32 +6956,32 @@
         <v>3</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
       <c r="V74" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="X74" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>42</v>
@@ -6992,7 +6999,7 @@
         <v>76</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="1"/>
@@ -7007,32 +7014,32 @@
         <v>10</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
       <c r="V75" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y75" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z75" s="2" t="s">
         <v>42</v>
@@ -7050,7 +7057,7 @@
         <v>74</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="1"/>
@@ -7065,32 +7072,32 @@
         <v>9</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
       <c r="V76" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X76" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y76" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="Y76" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>42</v>
@@ -7108,7 +7115,7 @@
         <v>75</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="1"/>
@@ -7123,32 +7130,32 @@
         <v>15</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
       <c r="V77" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z77" s="2" t="s">
         <v>42</v>
@@ -7166,7 +7173,7 @@
         <v>78</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="1"/>
@@ -7181,32 +7188,32 @@
         <v>2</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
       <c r="V78" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z78" s="2" t="s">
         <v>42</v>
@@ -7224,7 +7231,7 @@
         <v>77</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="1"/>
@@ -7239,32 +7246,32 @@
         <v>1</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
       <c r="V79" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y79" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z79" s="2" t="s">
         <v>42</v>
@@ -7282,7 +7289,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="1"/>
@@ -7306,23 +7313,23 @@
         <v>36</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
       <c r="V80" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>42</v>
@@ -7340,7 +7347,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="1"/>
@@ -7355,32 +7362,32 @@
         <v>17</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
       <c r="V81" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y81" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z81" s="2" t="s">
         <v>42</v>
@@ -7398,7 +7405,7 @@
         <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="1"/>
@@ -7413,32 +7420,32 @@
         <v>6</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
       <c r="T82" s="2"/>
       <c r="U82" s="2"/>
       <c r="V82" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z82" s="2" t="s">
         <v>42</v>
@@ -7456,7 +7463,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="1"/>
@@ -7471,32 +7478,32 @@
         <v>4</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="R83" s="2"/>
-      <c r="S83" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
       <c r="V83" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y83" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Z83" s="2" t="s">
         <v>42</v>
@@ -7514,7 +7521,7 @@
         <v>84</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="1"/>
@@ -7529,32 +7536,32 @@
         <v>3</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
       <c r="V84" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X84" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z84" s="2" t="s">
         <v>42</v>
@@ -7572,7 +7579,7 @@
         <v>83</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="1"/>
@@ -7587,32 +7594,32 @@
         <v>13</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
       <c r="V85" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z85" s="2" t="s">
         <v>42</v>
@@ -7630,7 +7637,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="1"/>
@@ -7645,32 +7652,32 @@
         <v>12</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
       <c r="V86" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z86" s="2" t="s">
         <v>42</v>
@@ -7688,7 +7695,7 @@
         <v>88</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="1"/>
@@ -7703,32 +7710,32 @@
         <v>2</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
       <c r="V87" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z87" s="2" t="s">
         <v>42</v>
@@ -7746,7 +7753,7 @@
         <v>86</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="1"/>
@@ -7761,32 +7768,32 @@
         <v>5</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
       <c r="V88" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z88" s="2" t="s">
         <v>42</v>
@@ -7804,7 +7811,7 @@
         <v>87</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="1"/>
@@ -7819,32 +7826,32 @@
         <v>8</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
       <c r="V89" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z89" s="2" t="s">
         <v>42</v>
@@ -7862,7 +7869,7 @@
         <v>90</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="1"/>
@@ -7877,32 +7884,32 @@
         <v>10</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
       <c r="V90" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z90" s="2" t="s">
         <v>42</v>
@@ -7920,7 +7927,7 @@
         <v>89</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="1"/>
@@ -7935,32 +7942,32 @@
         <v>7</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
       <c r="V91" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z91" s="2" t="s">
         <v>42</v>
@@ -7978,7 +7985,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="1"/>
@@ -7993,32 +8000,32 @@
         <v>1</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
       <c r="V92" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z92" s="2" t="s">
         <v>42</v>
@@ -8036,7 +8043,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="1"/>
@@ -8060,23 +8067,23 @@
         <v>36</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
       <c r="V93" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z93" s="2" t="s">
         <v>42</v>
@@ -8094,7 +8101,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="1"/>
@@ -8109,32 +8116,32 @@
         <v>2</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
       <c r="V94" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z94" s="2" t="s">
         <v>42</v>
@@ -8152,7 +8159,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="1"/>
@@ -8167,32 +8174,32 @@
         <v>6</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="R95" s="2"/>
-      <c r="S95" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
       <c r="V95" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z95" s="2" t="s">
         <v>42</v>
@@ -8210,7 +8217,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="1"/>
@@ -8225,32 +8232,32 @@
         <v>17</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="R96" s="2"/>
-      <c r="S96" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
       <c r="V96" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z96" s="2" t="s">
         <v>42</v>
@@ -8268,7 +8275,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="1"/>
@@ -8283,32 +8290,32 @@
         <v>12</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="R97" s="2"/>
-      <c r="S97" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
       <c r="V97" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z97" s="2" t="s">
         <v>42</v>
@@ -8326,7 +8333,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="1"/>
@@ -8341,32 +8348,32 @@
         <v>9</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="R98" s="2"/>
-      <c r="S98" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
       <c r="V98" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z98" s="2" t="s">
         <v>42</v>
@@ -8384,7 +8391,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="1"/>
@@ -8399,32 +8406,32 @@
         <v>3</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="R99" s="2"/>
-      <c r="S99" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
       <c r="V99" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X99" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z99" s="2" t="s">
         <v>42</v>
@@ -8442,7 +8449,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="1"/>
@@ -8457,32 +8464,32 @@
         <v>5</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="R100" s="2"/>
-      <c r="S100" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
       <c r="V100" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z100" s="2" t="s">
         <v>42</v>
@@ -8500,7 +8507,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="1"/>
@@ -8515,32 +8522,32 @@
         <v>8</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="R101" s="2"/>
-      <c r="S101" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
       <c r="V101" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z101" s="2" t="s">
         <v>42</v>
@@ -8558,7 +8565,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="1"/>
@@ -8573,32 +8580,32 @@
         <v>2</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="R102" s="2"/>
-      <c r="S102" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
       <c r="V102" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z102" s="2" t="s">
         <v>42</v>
@@ -8616,7 +8623,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="1"/>
@@ -8631,32 +8638,32 @@
         <v>17</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="R103" s="2"/>
-      <c r="S103" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
       <c r="V103" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="X103" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>42</v>
@@ -8674,7 +8681,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="1"/>
@@ -8689,32 +8696,32 @@
         <v>5</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="R104" s="2"/>
-      <c r="S104" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
       <c r="V104" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z104" s="2" t="s">
         <v>42</v>
@@ -8732,7 +8739,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="1"/>
@@ -8747,32 +8754,32 @@
         <v>1</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="R105" s="2"/>
-      <c r="S105" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
       <c r="V105" s="2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="X105" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z105" s="2" t="s">
         <v>42</v>

--- a/src/resultados_partidos.xlsx
+++ b/src/resultados_partidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="371">
   <si>
     <t>id</t>
   </si>
@@ -106,46 +106,52 @@
     <t>A</t>
   </si>
   <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>Estadio Azteca</t>
+  </si>
+  <si>
+    <t>Mexico City</t>
+  </si>
+  <si>
     <t>Mexico</t>
   </si>
   <si>
-    <t>MEX</t>
-  </si>
-  <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>RSA</t>
-  </si>
-  <si>
-    <t>Estadio Azteca</t>
-  </si>
-  <si>
-    <t>Mexico City</t>
-  </si>
-  <si>
     <t>11/06/2026</t>
   </si>
   <si>
     <t>completed</t>
   </si>
   <si>
-    <t>'</t>
+    <t>11 de junio</t>
+  </si>
+  <si>
+    <t>14:00</t>
   </si>
   <si>
     <t>Regular</t>
   </si>
   <si>
-    <t>Mexico vs South Africa</t>
-  </si>
-  <si>
-    <t>Korea Republic</t>
+    <t>México vs Sudáfrica</t>
+  </si>
+  <si>
+    <t>Corea del Sur</t>
   </si>
   <si>
     <t>KOR</t>
   </si>
   <si>
-    <t>Czechia</t>
+    <t>Chequia</t>
   </si>
   <si>
     <t>CZE</t>
@@ -157,42 +163,54 @@
     <t>Guadalajara</t>
   </si>
   <si>
-    <t>Korea Republic vs Czechia</t>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>Corea del Sur vs Chequia</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
+    <t>BMO Field</t>
+  </si>
+  <si>
+    <t>Toronto, ON</t>
+  </si>
+  <si>
     <t>Canada</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>Bosnia-Herzegovina</t>
-  </si>
-  <si>
-    <t>BIH</t>
-  </si>
-  <si>
-    <t>BMO Field</t>
-  </si>
-  <si>
-    <t>Toronto, ON</t>
-  </si>
-  <si>
     <t>12/06/2026</t>
   </si>
   <si>
+    <t>12 de junio</t>
+  </si>
+  <si>
     <t>Empate</t>
   </si>
   <si>
-    <t>Canada vs Bosnia-Herzegovina</t>
+    <t>Canadá vs Bosnia y Herzegovina</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
     <t>USA</t>
   </si>
   <si>
@@ -208,16 +226,19 @@
     <t>Inglewood, CA</t>
   </si>
   <si>
-    <t>USA vs Paraguay</t>
-  </si>
-  <si>
-    <t>Qatar</t>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Estados Unidos vs Paraguay</t>
+  </si>
+  <si>
+    <t>Catar</t>
   </si>
   <si>
     <t>QAT</t>
   </si>
   <si>
-    <t>Switzerland</t>
+    <t>Suiza</t>
   </si>
   <si>
     <t>SUI</t>
@@ -232,19 +253,22 @@
     <t>13/06/2026</t>
   </si>
   <si>
-    <t>Qatar vs Switzerland</t>
+    <t>13 de junio</t>
+  </si>
+  <si>
+    <t>Catar vs Suiza</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>Brazil</t>
+    <t>Brasil</t>
   </si>
   <si>
     <t>BRA</t>
   </si>
   <si>
-    <t>Morocco</t>
+    <t>Marruecos</t>
   </si>
   <si>
     <t>MAR</t>
@@ -256,16 +280,19 @@
     <t>East Rutherford, NJ</t>
   </si>
   <si>
-    <t>Brazil vs Morocco</t>
-  </si>
-  <si>
-    <t>Haiti</t>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Brasil vs Marruecos</t>
+  </si>
+  <si>
+    <t>Haití</t>
   </si>
   <si>
     <t>HAI</t>
   </si>
   <si>
-    <t>Scotland</t>
+    <t>Escocia</t>
   </si>
   <si>
     <t>SCO</t>
@@ -277,7 +304,7 @@
     <t>Foxborough, MA</t>
   </si>
   <si>
-    <t>Haiti vs Scotland</t>
+    <t>Haití vs Escocia</t>
   </si>
   <si>
     <t>Australia</t>
@@ -286,7 +313,7 @@
     <t>AUS</t>
   </si>
   <si>
-    <t>Turkey</t>
+    <t>Turquía</t>
   </si>
   <si>
     <t>TUR</t>
@@ -298,19 +325,22 @@
     <t>Vancouver, BC</t>
   </si>
   <si>
-    <t>Australia vs Turkey</t>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Australia vs Turquía</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>Germany</t>
+    <t>Alemania</t>
   </si>
   <si>
     <t>GER</t>
   </si>
   <si>
-    <t>Curaçao</t>
+    <t>Curazao</t>
   </si>
   <si>
     <t>CUW</t>
@@ -325,19 +355,25 @@
     <t>14/06/2026</t>
   </si>
   <si>
-    <t>Germany vs Curaçao</t>
+    <t>14 de junio</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>Alemania vs Curazao</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>Netherlands</t>
+    <t>Países Bajos</t>
   </si>
   <si>
     <t>NED</t>
   </si>
   <si>
-    <t>Japan</t>
+    <t>Japón</t>
   </si>
   <si>
     <t>JPN</t>
@@ -349,10 +385,13 @@
     <t>Arlington, TX</t>
   </si>
   <si>
-    <t>Netherlands vs Japan</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire</t>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>Países Bajos vs Japón</t>
+  </si>
+  <si>
+    <t>Costa de Marfil</t>
   </si>
   <si>
     <t>CIV</t>
@@ -370,16 +409,19 @@
     <t>Philadelphia, PA</t>
   </si>
   <si>
-    <t>Côte d'Ivoire vs Ecuador</t>
-  </si>
-  <si>
-    <t>Sweden</t>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>Costa de Marfil vs Ecuador</t>
+  </si>
+  <si>
+    <t>Suecia</t>
   </si>
   <si>
     <t>SWE</t>
   </si>
   <si>
-    <t>Tunisia</t>
+    <t>Túnez</t>
   </si>
   <si>
     <t>TUN</t>
@@ -391,13 +433,13 @@
     <t>Monterrey</t>
   </si>
   <si>
-    <t>Sweden vs Tunisia</t>
+    <t>Suecia vs Túnez</t>
   </si>
   <si>
     <t>H</t>
   </si>
   <si>
-    <t>Spain</t>
+    <t>España</t>
   </si>
   <si>
     <t>ESP</t>
@@ -418,19 +460,25 @@
     <t>15/06/2026</t>
   </si>
   <si>
-    <t>Spain vs Cabo Verde</t>
+    <t>15 de junio</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>España vs Cabo Verde</t>
   </si>
   <si>
     <t>G</t>
   </si>
   <si>
-    <t>Belgium</t>
+    <t>Bélgica</t>
   </si>
   <si>
     <t>BEL</t>
   </si>
   <si>
-    <t>Egypt</t>
+    <t>Egipto</t>
   </si>
   <si>
     <t>EGY</t>
@@ -442,10 +490,10 @@
     <t>Seattle, WA</t>
   </si>
   <si>
-    <t>Belgium vs Egypt</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
+    <t>Bélgica vs Egipto</t>
+  </si>
+  <si>
+    <t>Arabia Saudita</t>
   </si>
   <si>
     <t>KSA</t>
@@ -463,28 +511,28 @@
     <t>Miami Gardens, FL</t>
   </si>
   <si>
-    <t>Saudi Arabia vs Uruguay</t>
-  </si>
-  <si>
-    <t>IR Iran</t>
+    <t>Arabia Saudita vs Uruguay</t>
+  </si>
+  <si>
+    <t>Irán</t>
   </si>
   <si>
     <t>IRN</t>
   </si>
   <si>
-    <t>New Zealand</t>
+    <t>Nueva Zelanda</t>
   </si>
   <si>
     <t>NZL</t>
   </si>
   <si>
-    <t>IR Iran vs New Zealand</t>
+    <t>Irán vs Nueva Zelanda</t>
   </si>
   <si>
     <t>I</t>
   </si>
   <si>
-    <t>France</t>
+    <t>Francia</t>
   </si>
   <si>
     <t>FRA</t>
@@ -499,22 +547,25 @@
     <t>16/06/2026</t>
   </si>
   <si>
-    <t>France vs Senegal</t>
-  </si>
-  <si>
-    <t>Iraq</t>
+    <t>16 de junio</t>
+  </si>
+  <si>
+    <t>Francia vs Senegal</t>
+  </si>
+  <si>
+    <t>Irak</t>
   </si>
   <si>
     <t>IRQ</t>
   </si>
   <si>
-    <t>Norway</t>
+    <t>Noruega</t>
   </si>
   <si>
     <t>NOR</t>
   </si>
   <si>
-    <t>Iraq vs Norway</t>
+    <t>Irak vs Noruega</t>
   </si>
   <si>
     <t>J</t>
@@ -526,7 +577,7 @@
     <t>ARG</t>
   </si>
   <si>
-    <t>Algeria</t>
+    <t>Argelia</t>
   </si>
   <si>
     <t>ALG</t>
@@ -538,7 +589,7 @@
     <t>Kansas City, MO</t>
   </si>
   <si>
-    <t>Argentina vs Algeria</t>
+    <t>Argentina vs Argelia</t>
   </si>
   <si>
     <t>Austria</t>
@@ -547,13 +598,13 @@
     <t>AUT</t>
   </si>
   <si>
-    <t>Jordan</t>
+    <t>Jordania</t>
   </si>
   <si>
     <t>JOR</t>
   </si>
   <si>
-    <t>Austria vs Jordan</t>
+    <t>Austria vs Jordania</t>
   </si>
   <si>
     <t>K</t>
@@ -565,7 +616,7 @@
     <t>POR</t>
   </si>
   <si>
-    <t>Congo DR</t>
+    <t>RD del Congo</t>
   </si>
   <si>
     <t>COD</t>
@@ -574,25 +625,28 @@
     <t>17/06/2026</t>
   </si>
   <si>
-    <t>Portugal vs Congo DR</t>
+    <t>17 de junio</t>
+  </si>
+  <si>
+    <t>Portugal vs RD del Congo</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>England</t>
+    <t>Inglaterra</t>
   </si>
   <si>
     <t>ENG</t>
   </si>
   <si>
-    <t>Croatia</t>
+    <t>Croacia</t>
   </si>
   <si>
     <t>CRO</t>
   </si>
   <si>
-    <t>England vs Croatia</t>
+    <t>Inglaterra vs Croacia</t>
   </si>
   <si>
     <t>Ghana</t>
@@ -601,16 +655,16 @@
     <t>GHA</t>
   </si>
   <si>
-    <t>Panama</t>
+    <t>Panamá</t>
   </si>
   <si>
     <t>PAN</t>
   </si>
   <si>
-    <t>Ghana vs Panama</t>
-  </si>
-  <si>
-    <t>Uzbekistan</t>
+    <t>Ghana vs Panamá</t>
+  </si>
+  <si>
+    <t>Uzbekistán</t>
   </si>
   <si>
     <t>UZB</t>
@@ -622,136 +676,172 @@
     <t>COL</t>
   </si>
   <si>
-    <t>Uzbekistan vs Colombia</t>
+    <t>Uzbekistán vs Colombia</t>
   </si>
   <si>
     <t>18/06/2026</t>
   </si>
   <si>
-    <t>Czechia vs South Africa</t>
-  </si>
-  <si>
-    <t>Switzerland vs Bosnia-Herzegovina</t>
-  </si>
-  <si>
-    <t>Canada vs Qatar</t>
-  </si>
-  <si>
-    <t>Mexico vs Korea Republic</t>
+    <t>18 de junio</t>
+  </si>
+  <si>
+    <t>Chequia vs Sudáfrica</t>
+  </si>
+  <si>
+    <t>Suiza vs Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t>Canadá vs Catar</t>
+  </si>
+  <si>
+    <t>México vs Corea del Sur</t>
   </si>
   <si>
     <t>19/06/2026</t>
   </si>
   <si>
-    <t>USA vs Australia</t>
-  </si>
-  <si>
-    <t>Scotland vs Morocco</t>
-  </si>
-  <si>
-    <t>Brazil vs Haiti</t>
-  </si>
-  <si>
-    <t>Turkey vs Paraguay</t>
+    <t>19 de junio</t>
+  </si>
+  <si>
+    <t>Estados Unidos vs Australia</t>
+  </si>
+  <si>
+    <t>Escocia vs Marruecos</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>Brasil vs Haití</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>Turquía vs Paraguay</t>
   </si>
   <si>
     <t>20/06/2026</t>
   </si>
   <si>
-    <t>Netherlands vs Sweden</t>
-  </si>
-  <si>
-    <t>Germany vs Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>Ecuador vs Curaçao</t>
-  </si>
-  <si>
-    <t>Tunisia vs Japan</t>
+    <t>20 de junio</t>
+  </si>
+  <si>
+    <t>Países Bajos vs Suecia</t>
+  </si>
+  <si>
+    <t>Alemania vs Costa de Marfil</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Ecuador vs Curazao</t>
+  </si>
+  <si>
+    <t>Túnez vs Japón</t>
   </si>
   <si>
     <t>21/06/2026</t>
   </si>
   <si>
-    <t>Spain vs Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Belgium vs IR Iran</t>
+    <t>21 de junio</t>
+  </si>
+  <si>
+    <t>España vs Arabia Saudita</t>
+  </si>
+  <si>
+    <t>Bélgica vs Irán</t>
   </si>
   <si>
     <t>Uruguay vs Cabo Verde</t>
   </si>
   <si>
-    <t>New Zealand vs Egypt</t>
+    <t>Nueva Zelanda vs Egipto</t>
   </si>
   <si>
     <t>22/06/2026</t>
   </si>
   <si>
+    <t>22 de junio</t>
+  </si>
+  <si>
     <t>Argentina vs Austria</t>
   </si>
   <si>
-    <t>France vs Iraq</t>
-  </si>
-  <si>
-    <t>Norway vs Senegal</t>
-  </si>
-  <si>
-    <t>Jordan vs Algeria</t>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>Francia vs Irak</t>
+  </si>
+  <si>
+    <t>Noruega vs Senegal</t>
+  </si>
+  <si>
+    <t>Jordania vs Argelia</t>
   </si>
   <si>
     <t>23/06/2026</t>
   </si>
   <si>
-    <t>Portugal vs Uzbekistan</t>
-  </si>
-  <si>
-    <t>England vs Ghana</t>
-  </si>
-  <si>
-    <t>Panama vs Croatia</t>
-  </si>
-  <si>
-    <t>Colombia vs Congo DR</t>
+    <t>23 de junio</t>
+  </si>
+  <si>
+    <t>Portugal vs Uzbekistán</t>
+  </si>
+  <si>
+    <t>Inglaterra vs Ghana</t>
+  </si>
+  <si>
+    <t>Panamá vs Croacia</t>
+  </si>
+  <si>
+    <t>Colombia vs RD del Congo</t>
   </si>
   <si>
     <t>24/06/2026</t>
   </si>
   <si>
-    <t>Bosnia-Herzegovina vs Qatar</t>
-  </si>
-  <si>
-    <t>Switzerland vs Canada</t>
-  </si>
-  <si>
-    <t>Scotland vs Brazil</t>
-  </si>
-  <si>
-    <t>Morocco vs Haiti</t>
-  </si>
-  <si>
-    <t>Czechia vs Mexico</t>
-  </si>
-  <si>
-    <t>South Africa vs Korea Republic</t>
+    <t>24 de junio</t>
+  </si>
+  <si>
+    <t>Bosnia y Herzegovina vs Catar</t>
+  </si>
+  <si>
+    <t>Suiza vs Canadá</t>
+  </si>
+  <si>
+    <t>Escocia vs Brasil</t>
+  </si>
+  <si>
+    <t>Marruecos vs Haití</t>
+  </si>
+  <si>
+    <t>Chequia vs México</t>
+  </si>
+  <si>
+    <t>Sudáfrica vs Corea del Sur</t>
   </si>
   <si>
     <t>25/06/2026</t>
   </si>
   <si>
-    <t>Curaçao vs Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>Ecuador vs Germany</t>
-  </si>
-  <si>
-    <t>Tunisia vs Netherlands</t>
-  </si>
-  <si>
-    <t>Japan vs Sweden</t>
-  </si>
-  <si>
-    <t>Turkey vs USA</t>
+    <t>25 de junio</t>
+  </si>
+  <si>
+    <t>Curazao vs Costa de Marfil</t>
+  </si>
+  <si>
+    <t>Ecuador vs Alemania</t>
+  </si>
+  <si>
+    <t>Túnez vs Países Bajos</t>
+  </si>
+  <si>
+    <t>Japón vs Suecia</t>
+  </si>
+  <si>
+    <t>Turquía vs Estados Unidos</t>
   </si>
   <si>
     <t>Paraguay vs Australia</t>
@@ -760,43 +850,52 @@
     <t>26/06/2026</t>
   </si>
   <si>
-    <t>Senegal vs Iraq</t>
-  </si>
-  <si>
-    <t>Norway vs France</t>
-  </si>
-  <si>
-    <t>Cabo Verde vs Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Uruguay vs Spain</t>
-  </si>
-  <si>
-    <t>Egypt vs IR Iran</t>
-  </si>
-  <si>
-    <t>New Zealand vs Belgium</t>
+    <t>26 de junio</t>
+  </si>
+  <si>
+    <t>Senegal vs Irak</t>
+  </si>
+  <si>
+    <t>Noruega vs Francia</t>
+  </si>
+  <si>
+    <t>Cabo Verde vs Arabia Saudita</t>
+  </si>
+  <si>
+    <t>Uruguay vs España</t>
+  </si>
+  <si>
+    <t>Egipto vs Irán</t>
+  </si>
+  <si>
+    <t>Nueva Zelanda vs Bélgica</t>
   </si>
   <si>
     <t>27/06/2026</t>
   </si>
   <si>
-    <t>Panama vs England</t>
-  </si>
-  <si>
-    <t>Croatia vs Ghana</t>
-  </si>
-  <si>
-    <t>Congo DR vs Uzbekistan</t>
+    <t>27 de junio</t>
+  </si>
+  <si>
+    <t>Panamá vs Inglaterra</t>
+  </si>
+  <si>
+    <t>Croacia vs Ghana</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>RD del Congo vs Uzbekistán</t>
   </si>
   <si>
     <t>Colombia vs Portugal</t>
   </si>
   <si>
-    <t>Algeria vs Austria</t>
-  </si>
-  <si>
-    <t>Jordan vs Argentina</t>
+    <t>Argelia vs Austria</t>
+  </si>
+  <si>
+    <t>Jordania vs Argentina</t>
   </si>
   <si>
     <t>R32</t>
@@ -805,79 +904,112 @@
     <t>28/06/2026</t>
   </si>
   <si>
-    <t>South Africa vs Canada</t>
+    <t>28 de junio</t>
+  </si>
+  <si>
+    <t>Sudáfrica vs Canadá</t>
   </si>
   <si>
     <t>29/06/2026</t>
   </si>
   <si>
+    <t>29 de junio</t>
+  </si>
+  <si>
     <t>Penales</t>
   </si>
   <si>
-    <t>Netherlands vs Morocco</t>
-  </si>
-  <si>
-    <t>Brazil vs Japan</t>
-  </si>
-  <si>
-    <t>Germany vs Paraguay</t>
+    <t>Países Bajos vs Marruecos</t>
+  </si>
+  <si>
+    <t>Brasil vs Japón</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>Alemania vs Paraguay</t>
   </si>
   <si>
     <t>30/06/2026</t>
   </si>
   <si>
-    <t>France vs Sweden</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire vs Norway</t>
-  </si>
-  <si>
-    <t>Mexico vs Ecuador</t>
+    <t>30 de junio</t>
+  </si>
+  <si>
+    <t>Francia vs Suecia</t>
+  </si>
+  <si>
+    <t>Costa de Marfil vs Noruega</t>
+  </si>
+  <si>
+    <t>México vs Ecuador</t>
   </si>
   <si>
     <t>01/07/2026</t>
   </si>
   <si>
-    <t>in_progress</t>
-  </si>
-  <si>
-    <t>En vivo</t>
-  </si>
-  <si>
-    <t>England vs Congo DR</t>
+    <t>1 de julio</t>
+  </si>
+  <si>
+    <t>1/07/2026</t>
+  </si>
+  <si>
+    <t>Inglaterra vs RD del Congo</t>
+  </si>
+  <si>
+    <t>Estados Unidos vs Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t>Tiempo extra</t>
+  </si>
+  <si>
+    <t>Bélgica vs Senegal</t>
+  </si>
+  <si>
+    <t>02/07/2026</t>
+  </si>
+  <si>
+    <t>2 de julio</t>
+  </si>
+  <si>
+    <t>2/07/2026</t>
+  </si>
+  <si>
+    <t>Portugal vs Croacia</t>
+  </si>
+  <si>
+    <t>España vs Austria</t>
+  </si>
+  <si>
+    <t>Suiza vs Argelia</t>
+  </si>
+  <si>
+    <t>03/07/2026</t>
   </si>
   <si>
     <t>scheduled</t>
   </si>
   <si>
+    <t>3 de julio</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>3/07/2026</t>
+  </si>
+  <si>
     <t>Por jugar</t>
   </si>
   <si>
-    <t>USA vs Bosnia-Herzegovina</t>
-  </si>
-  <si>
-    <t>Belgium vs Senegal</t>
-  </si>
-  <si>
-    <t>02/07/2026</t>
-  </si>
-  <si>
-    <t>Portugal vs Croatia</t>
-  </si>
-  <si>
-    <t>Spain vs Austria</t>
-  </si>
-  <si>
-    <t>Switzerland vs Algeria</t>
-  </si>
-  <si>
-    <t>03/07/2026</t>
-  </si>
-  <si>
     <t>Colombia vs Ghana</t>
   </si>
   <si>
-    <t>Australia vs Egypt</t>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Australia vs Egipto</t>
   </si>
   <si>
     <t>Argentina vs Cabo Verde</t>
@@ -889,58 +1021,112 @@
     <t>04/07/2026</t>
   </si>
   <si>
-    <t>Paraguay vs France</t>
-  </si>
-  <si>
-    <t>Canada vs Morocco</t>
+    <t>4 de julio</t>
+  </si>
+  <si>
+    <t>4/07/2026</t>
+  </si>
+  <si>
+    <t>Paraguay vs Francia</t>
+  </si>
+  <si>
+    <t>Canadá vs Marruecos</t>
   </si>
   <si>
     <t>05/07/2026</t>
   </si>
   <si>
-    <t>Brazil vs Norway</t>
+    <t>5 de julio</t>
+  </si>
+  <si>
+    <t>5/07/2026</t>
+  </si>
+  <si>
+    <t>Brasil vs Noruega</t>
+  </si>
+  <si>
+    <t>México vs Inglaterra</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>6 de julio</t>
+  </si>
+  <si>
+    <t>6/07/2026</t>
   </si>
   <si>
     <t>Por definir vs Por definir</t>
   </si>
   <si>
-    <t>06/07/2026</t>
+    <t>Estados Unidos vs Bélgica</t>
   </si>
   <si>
     <t>07/07/2026</t>
   </si>
   <si>
+    <t>7 de julio</t>
+  </si>
+  <si>
+    <t>7/07/2026</t>
+  </si>
+  <si>
     <t>QF</t>
   </si>
   <si>
     <t>09/07/2026</t>
   </si>
   <si>
+    <t>9 de julio</t>
+  </si>
+  <si>
+    <t>9/07/2026</t>
+  </si>
+  <si>
     <t>10/07/2026</t>
   </si>
   <si>
+    <t>10 de julio</t>
+  </si>
+  <si>
     <t>11/07/2026</t>
   </si>
   <si>
+    <t>11 de julio</t>
+  </si>
+  <si>
     <t>SF</t>
   </si>
   <si>
     <t>14/07/2026</t>
   </si>
   <si>
+    <t>14 de julio</t>
+  </si>
+  <si>
     <t>15/07/2026</t>
   </si>
   <si>
+    <t>15 de julio</t>
+  </si>
+  <si>
     <t>3rd</t>
   </si>
   <si>
     <t>18/07/2026</t>
   </si>
   <si>
+    <t>18 de julio</t>
+  </si>
+  <si>
     <t>final</t>
   </si>
   <si>
     <t>19/07/2026</t>
+  </si>
+  <si>
+    <t>19 de julio</t>
   </si>
 </sst>
 </file>
@@ -1455,10 +1641,10 @@
         <v>35</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="1">
         <v>2</v>
@@ -1469,21 +1655,25 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y2" s="2"/>
       <c r="Z2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -1503,36 +1693,36 @@
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="1">
         <v>4</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="1">
         <v>16</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R3" s="1">
         <v>2</v>
@@ -1543,21 +1733,25 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y3" s="2"/>
       <c r="Z3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -1571,42 +1765,42 @@
         <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="1">
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="1">
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R4" s="1">
         <v>1</v>
@@ -1617,21 +1811,25 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="X4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y4" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="Z4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -1645,42 +1843,42 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E5" s="1">
         <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="1">
         <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="1">
         <v>3</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="R5" s="1">
         <v>4</v>
@@ -1691,21 +1889,25 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W5" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="X5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y5" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="Z5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -1719,42 +1921,42 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1">
         <v>7</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="1">
         <v>4</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R6" s="1">
         <v>1</v>
@@ -1765,21 +1967,25 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W6" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="X6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y6" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="Z6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -1793,42 +1999,42 @@
         <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1">
         <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="1">
         <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="1">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="R7" s="1">
         <v>1</v>
@@ -1839,21 +2045,25 @@
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W7" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="X7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y7" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="Z7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -1867,42 +2077,42 @@
         <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="1">
         <v>11</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="1">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -1913,21 +2123,25 @@
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W8" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="X8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y8" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="Z8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -1941,42 +2155,42 @@
         <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E9" s="1">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="1">
         <v>16</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="1">
         <v>12</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="R9" s="1">
         <v>2</v>
@@ -1987,21 +2201,25 @@
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W9" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="X9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y9" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="Z9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -2015,42 +2233,42 @@
         <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E10" s="1">
         <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="1">
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="1">
         <v>10</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R10" s="1">
         <v>7</v>
@@ -2061,21 +2279,25 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W10" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="X10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y10" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="Z10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2089,42 +2311,42 @@
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E11" s="1">
         <v>21</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="1">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="1">
         <v>2</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R11" s="1">
         <v>2</v>
@@ -2135,21 +2357,25 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W11" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="X11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y11" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="Z11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -2163,42 +2389,42 @@
         <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E12" s="1">
         <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="1">
         <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="1">
         <v>7</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R12" s="1">
         <v>1</v>
@@ -2209,21 +2435,25 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W12" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="X12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="Z12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -2237,42 +2467,42 @@
         <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E13" s="1">
         <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="1">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="1">
         <v>15</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="R13" s="1">
         <v>5</v>
@@ -2283,21 +2513,25 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W13" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="X13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="Z13" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -2311,42 +2545,42 @@
         <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E14" s="1">
         <v>30</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="1">
         <v>32</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="1">
         <v>17</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="R14" s="1">
         <v>0</v>
@@ -2357,21 +2591,25 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W14" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="X14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="Z14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -2385,42 +2623,42 @@
         <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E15" s="1">
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="1">
         <v>26</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="1">
         <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="R15" s="1">
         <v>1</v>
@@ -2431,21 +2669,25 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W15" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="X15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="Z15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -2459,42 +2701,42 @@
         <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E16" s="1">
         <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="1">
         <v>31</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="1">
         <v>5</v>
       </c>
       <c r="N16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="R16" s="1">
         <v>1</v>
@@ -2505,21 +2747,25 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W16" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="X16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="Z16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:28">
@@ -2533,42 +2779,42 @@
         <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E17" s="1">
         <v>27</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="1">
         <v>28</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="1">
         <v>3</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="R17" s="1">
         <v>2</v>
@@ -2579,21 +2825,25 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W17" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="X17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="Z17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -2607,42 +2857,42 @@
         <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E18" s="1">
         <v>33</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="1">
         <v>34</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="1">
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="R18" s="1">
         <v>3</v>
@@ -2653,21 +2903,25 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W18" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="X18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="Z18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -2681,42 +2935,42 @@
         <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E19" s="1">
         <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="1">
         <v>35</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="1">
         <v>9</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="R19" s="1">
         <v>1</v>
@@ -2727,21 +2981,25 @@
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="X19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="Z19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:28">
@@ -2755,42 +3013,42 @@
         <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E20" s="1">
         <v>37</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="1">
         <v>38</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="1">
         <v>8</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="R20" s="1">
         <v>3</v>
@@ -2801,21 +3059,25 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W20" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="X20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="Z20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:28">
@@ -2829,42 +3091,42 @@
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E21" s="1">
         <v>39</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="1">
         <v>40</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="1">
         <v>4</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="R21" s="1">
         <v>3</v>
@@ -2875,21 +3137,25 @@
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W21" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="X21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="Z21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:28">
@@ -2903,42 +3169,42 @@
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E22" s="1">
         <v>41</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="1">
         <v>44</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="1">
         <v>10</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="R22" s="1">
         <v>1</v>
@@ -2949,21 +3215,25 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W22" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="X22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="Z22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:28">
@@ -2977,42 +3247,42 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E23" s="1">
         <v>47</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="1">
         <v>48</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="1">
         <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="R23" s="1">
         <v>4</v>
@@ -3023,21 +3293,25 @@
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W23" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="X23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="Z23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:28">
@@ -3051,42 +3325,42 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E24" s="1">
         <v>45</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="1">
         <v>46</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="1">
         <v>13</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="R24" s="1">
         <v>1</v>
@@ -3097,21 +3371,25 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
       <c r="V24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W24" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="X24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="Z24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -3125,26 +3403,26 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E25" s="1">
         <v>42</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="1">
         <v>43</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="1">
@@ -3157,10 +3435,10 @@
         <v>35</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="R25" s="1">
         <v>1</v>
@@ -3171,21 +3449,25 @@
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W25" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="X25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="Z25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:28">
@@ -3205,10 +3487,10 @@
         <v>4</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="1">
@@ -3225,16 +3507,16 @@
         <v>17</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="R26" s="1">
         <v>1</v>
@@ -3245,21 +3527,25 @@
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W26" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="X26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="Z26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:28">
@@ -3273,42 +3559,42 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E27" s="1">
         <v>7</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="1">
         <v>8</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="1">
         <v>3</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="R27" s="1">
         <v>4</v>
@@ -3319,21 +3605,25 @@
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W27" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="X27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="Z27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:28">
@@ -3347,42 +3637,42 @@
         <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="1">
         <v>6</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="1">
         <v>12</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="R28" s="1">
         <v>6</v>
@@ -3393,21 +3683,25 @@
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W28" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="X28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="Z28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:28">
@@ -3437,26 +3731,26 @@
         <v>2</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="1">
         <v>16</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="R29" s="1">
         <v>1</v>
@@ -3467,21 +3761,25 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W29" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="X29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="Z29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:28">
@@ -3495,42 +3793,42 @@
         <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E30" s="1">
         <v>13</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="1">
         <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="1">
         <v>6</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="R30" s="1">
         <v>2</v>
@@ -3541,21 +3839,25 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W30" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="X30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="Z30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -3569,42 +3871,42 @@
         <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E31" s="1">
         <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="1">
         <v>12</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="1">
         <v>9</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="R31" s="1">
         <v>0</v>
@@ -3615,21 +3917,25 @@
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W31" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="X31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="Z31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:28">
@@ -3643,42 +3949,42 @@
         <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E32" s="1">
         <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="1">
         <v>10</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="1">
         <v>7</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="R32" s="1">
         <v>3</v>
@@ -3689,21 +3995,25 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
       <c r="V32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W32" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="X32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="Z32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:28">
@@ -3717,42 +4027,42 @@
         <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E33" s="1">
         <v>16</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="1">
         <v>15</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="1">
         <v>4</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -3763,21 +4073,25 @@
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
       <c r="V33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W33" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="X33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="Z33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -3791,42 +4105,42 @@
         <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E34" s="1">
         <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="1">
         <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="1">
         <v>10</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="R34" s="1">
         <v>5</v>
@@ -3837,21 +4151,25 @@
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
       <c r="V34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W34" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="X34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="Z34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:28">
@@ -3865,42 +4183,42 @@
         <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E35" s="1">
         <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="1">
         <v>17</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="1">
         <v>13</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="R35" s="1">
         <v>2</v>
@@ -3911,21 +4229,25 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W35" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="X35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="Z35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:28">
@@ -3939,42 +4261,42 @@
         <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E36" s="1">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="1">
         <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="1">
         <v>8</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="R36" s="1">
         <v>0</v>
@@ -3985,21 +4307,25 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W36" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="X36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="Z36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:28">
@@ -4013,42 +4339,42 @@
         <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E37" s="1">
         <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="1">
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="1">
         <v>15</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
@@ -4059,21 +4385,25 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W37" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="X37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="Z37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:28">
@@ -4087,42 +4417,42 @@
         <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E38" s="1">
         <v>30</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="1">
         <v>29</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="1">
         <v>17</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="R38" s="1">
         <v>4</v>
@@ -4133,21 +4463,25 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W38" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="X38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Z38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA38" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:28">
@@ -4161,42 +4495,42 @@
         <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E39" s="1">
         <v>25</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="1">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="1">
         <v>3</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="R39" s="1">
         <v>0</v>
@@ -4207,21 +4541,25 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W39" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="X39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Z39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA39" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:28">
@@ -4235,42 +4573,42 @@
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E40" s="1">
         <v>31</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="1">
         <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="1">
         <v>5</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="R40" s="1">
         <v>2</v>
@@ -4281,21 +4619,25 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W40" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="X40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Z40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA40" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:28">
@@ -4309,42 +4651,42 @@
         <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E41" s="1">
         <v>28</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="1">
         <v>26</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="1">
         <v>12</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="R41" s="1">
         <v>1</v>
@@ -4355,21 +4697,25 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W41" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="X41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="Z41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA41" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:28">
@@ -4383,42 +4729,42 @@
         <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E42" s="1">
         <v>37</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="1">
         <v>39</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="1">
         <v>2</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="R42" s="1">
         <v>2</v>
@@ -4429,21 +4775,25 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W42" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="X42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="Z42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA42" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:28">
@@ -4457,42 +4807,42 @@
         <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E43" s="1">
         <v>33</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="1">
         <v>36</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="R43" s="1">
         <v>3</v>
@@ -4503,21 +4853,25 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W43" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="X43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="Z43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA43" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:28">
@@ -4531,42 +4885,42 @@
         <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E44" s="1">
         <v>35</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="1">
         <v>34</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="1">
         <v>1</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="R44" s="1">
         <v>3</v>
@@ -4577,21 +4931,25 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W44" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="X44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="Z44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA44" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:28">
@@ -4605,42 +4963,42 @@
         <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E45" s="1">
         <v>40</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="1">
         <v>38</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="1">
         <v>4</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="R45" s="1">
         <v>1</v>
@@ -4651,21 +5009,25 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W45" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="X45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="Z45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA45" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:28">
@@ -4679,42 +5041,42 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E46" s="1">
         <v>41</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="1">
         <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="1">
         <v>10</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="R46" s="1">
         <v>5</v>
@@ -4725,21 +5087,25 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W46" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="X46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y46" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="Z46" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA46" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:28">
@@ -4753,42 +5119,42 @@
         <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E47" s="1">
         <v>47</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="1">
         <v>45</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="1">
         <v>9</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="R47" s="1">
         <v>0</v>
@@ -4799,21 +5165,25 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W47" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="X47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y47" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="Z47" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA47" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:28">
@@ -4827,42 +5197,42 @@
         <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E48" s="1">
         <v>46</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="1">
         <v>48</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="1">
         <v>13</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="R48" s="1">
         <v>0</v>
@@ -4873,21 +5243,25 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W48" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="X48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="Z48" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA48" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:28">
@@ -4901,42 +5275,42 @@
         <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E49" s="1">
         <v>43</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="1">
         <v>44</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="1">
         <v>16</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="R49" s="1">
         <v>1</v>
@@ -4947,21 +5321,25 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W49" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="X49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y49" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="Z49" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA49" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:28">
@@ -4975,42 +5353,42 @@
         <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="1">
         <v>6</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="1">
         <v>6</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R50" s="1">
         <v>3</v>
@@ -5021,21 +5399,25 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W50" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X50" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z50" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA50" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
     </row>
     <row r="51" spans="1:28">
@@ -5049,42 +5431,42 @@
         <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E51" s="1">
         <v>7</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="1">
         <v>12</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R51" s="1">
         <v>2</v>
@@ -5095,21 +5477,25 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W51" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X51" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z51" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA51" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:28">
@@ -5123,42 +5509,42 @@
         <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E52" s="1">
         <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="1">
         <v>9</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="1">
         <v>5</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R52" s="1">
         <v>0</v>
@@ -5169,21 +5555,25 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W52" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X52" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z52" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA52" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:28">
@@ -5197,42 +5587,42 @@
         <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E53" s="1">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="1">
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="1">
         <v>17</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R53" s="1">
         <v>4</v>
@@ -5243,21 +5633,25 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W53" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X53" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y53" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z53" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA53" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54" spans="1:28">
@@ -5277,10 +5671,10 @@
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="1">
@@ -5303,10 +5697,10 @@
         <v>35</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R54" s="1">
         <v>0</v>
@@ -5317,21 +5711,25 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W54" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X54" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y54" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z54" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
     </row>
     <row r="55" spans="1:28">
@@ -5361,26 +5759,26 @@
         <v>2</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="1">
         <v>15</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="R55" s="1">
         <v>1</v>
@@ -5391,21 +5789,25 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W55" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="X55" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Z55" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA55" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AB55" s="2" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56" spans="1:28">
@@ -5419,42 +5821,42 @@
         <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E56" s="1">
         <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="1">
         <v>17</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="1">
         <v>7</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -5465,21 +5867,25 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W56" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y56" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z56" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA56" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
     </row>
     <row r="57" spans="1:28">
@@ -5493,42 +5899,42 @@
         <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E57" s="1">
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="1">
         <v>19</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="1">
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R57" s="1">
         <v>2</v>
@@ -5539,21 +5945,25 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W57" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z57" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA57" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:28">
@@ -5567,42 +5977,42 @@
         <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E58" s="1">
         <v>23</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="1">
         <v>21</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="1">
         <v>8</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R58" s="1">
         <v>1</v>
@@ -5613,21 +6023,25 @@
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W58" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z58" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA58" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:28">
@@ -5641,42 +6055,42 @@
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E59" s="1">
         <v>22</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="1">
         <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="1">
         <v>2</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R59" s="1">
         <v>1</v>
@@ -5687,21 +6101,25 @@
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W59" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y59" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z59" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA59" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:28">
@@ -5715,42 +6133,42 @@
         <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E60" s="1">
         <v>16</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="1">
         <v>13</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="1">
         <v>3</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R60" s="1">
         <v>3</v>
@@ -5761,21 +6179,25 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W60" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y60" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z60" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA60" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -5789,42 +6211,42 @@
         <v>28</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E61" s="1">
         <v>15</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="1">
         <v>14</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="1">
         <v>4</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="R61" s="1">
         <v>0</v>
@@ -5835,21 +6257,25 @@
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W61" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="X61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y61" s="2" t="s">
+        <v>269</v>
+      </c>
       <c r="Z61" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA61" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -5863,42 +6289,42 @@
         <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E62" s="1">
         <v>34</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="1">
         <v>36</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="1">
         <v>13</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R62" s="1">
         <v>5</v>
@@ -5909,21 +6335,25 @@
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W62" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z62" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA62" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -5937,42 +6367,42 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E63" s="1">
         <v>35</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="1">
         <v>33</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="1">
         <v>9</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R63" s="1">
         <v>1</v>
@@ -5983,21 +6413,25 @@
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W63" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z63" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA63" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -6011,42 +6445,42 @@
         <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1">
         <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="1">
         <v>29</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="1">
         <v>10</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R64" s="1">
         <v>0</v>
@@ -6057,21 +6491,25 @@
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W64" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z64" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA64" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:28">
@@ -6085,42 +6523,42 @@
         <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1">
         <v>31</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="1">
         <v>30</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="1">
         <v>16</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R65" s="1">
         <v>0</v>
@@ -6131,21 +6569,25 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W65" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y65" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z65" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA65" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="1:28">
@@ -6159,42 +6601,42 @@
         <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E66" s="1">
         <v>26</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="1">
         <v>27</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="1">
         <v>6</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R66" s="1">
         <v>1</v>
@@ -6205,21 +6647,25 @@
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W66" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z66" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA66" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -6233,42 +6679,42 @@
         <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E67" s="1">
         <v>28</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="1">
         <v>25</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="1">
         <v>12</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="R67" s="1">
         <v>1</v>
@@ -6279,21 +6725,25 @@
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W67" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="X67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="Y67" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="Z67" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA67" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="68" spans="1:28">
@@ -6307,42 +6757,42 @@
         <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E68" s="1">
         <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="1">
         <v>47</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="1">
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R68" s="1">
         <v>0</v>
@@ -6353,21 +6803,25 @@
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W68" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X68" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y68" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z68" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA68" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:28">
@@ -6381,42 +6835,42 @@
         <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E69" s="1">
         <v>48</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="1">
         <v>45</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="1">
         <v>7</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R69" s="1">
         <v>2</v>
@@ -6427,21 +6881,25 @@
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W69" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y69" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z69" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA69" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="AB69" s="2" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -6455,42 +6913,42 @@
         <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E70" s="1">
         <v>44</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="1">
         <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="1">
         <v>17</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R70" s="1">
         <v>3</v>
@@ -6501,21 +6959,25 @@
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W70" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z70" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA70" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="AB70" s="2" t="s">
-        <v>257</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -6529,42 +6991,42 @@
         <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E71" s="1">
         <v>43</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="1">
         <v>41</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="1">
         <v>5</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R71" s="1">
         <v>0</v>
@@ -6575,21 +7037,25 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W71" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X71" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="Y71" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z71" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA71" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB71" s="2" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:28">
@@ -6603,42 +7069,42 @@
         <v>28</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E72" s="1">
         <v>38</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="1">
         <v>39</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="1">
         <v>8</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R72" s="1">
         <v>3</v>
@@ -6649,21 +7115,25 @@
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W72" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X72" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y72" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z72" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -6677,42 +7147,42 @@
         <v>28</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E73" s="1">
         <v>40</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="1">
         <v>37</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="1">
         <v>2</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="R73" s="1">
         <v>1</v>
@@ -6723,21 +7193,25 @@
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W73" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="X73" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="Z73" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA73" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="AB73" s="2" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:28">
@@ -6748,7 +7222,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="1">
@@ -6765,26 +7239,26 @@
         <v>5</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="1">
         <v>3</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="R74" s="1">
         <v>0</v>
@@ -6795,21 +7269,25 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W74" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="X74" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y74" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="Z74" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA74" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AB74" s="2" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:28">
@@ -6820,43 +7298,43 @@
         <v>76</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="1">
         <v>21</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="1">
         <v>12</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="1">
         <v>10</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="R75" s="1">
         <v>1</v>
@@ -6871,21 +7349,25 @@
         <v>3</v>
       </c>
       <c r="V75" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W75" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="X75" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y75" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="Z75" s="2" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="AA75" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AB75" s="2" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
     </row>
     <row r="76" spans="1:28">
@@ -6896,43 +7378,43 @@
         <v>74</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="1">
         <v>9</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="1">
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="1">
         <v>9</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="R76" s="1">
         <v>2</v>
@@ -6943,21 +7425,25 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W76" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="X76" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y76" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="Z76" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA76" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AB76" s="2" t="s">
-        <v>267</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77" spans="1:28">
@@ -6968,43 +7454,43 @@
         <v>75</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="1">
         <v>19</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="1">
         <v>15</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="1">
         <v>15</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="R77" s="1">
         <v>1</v>
@@ -7019,21 +7505,25 @@
         <v>4</v>
       </c>
       <c r="V77" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W77" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="X77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="Z77" s="2" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="AA77" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AB77" s="2" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:28">
@@ -7044,43 +7534,43 @@
         <v>78</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="1">
         <v>33</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="1">
         <v>24</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="1">
         <v>2</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="R78" s="1">
         <v>3</v>
@@ -7091,21 +7581,25 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W78" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="X78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y78" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="Z78" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA78" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="AB78" s="2" t="s">
-        <v>270</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:28">
@@ -7116,43 +7610,43 @@
         <v>77</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="1">
         <v>17</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="1">
         <v>35</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="1">
         <v>1</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="R79" s="1">
         <v>1</v>
@@ -7163,21 +7657,25 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W79" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="X79" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y79" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="Z79" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA79" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AB79" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:28">
@@ -7188,7 +7686,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="1">
@@ -7205,10 +7703,10 @@
         <v>18</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="1">
@@ -7221,10 +7719,10 @@
         <v>35</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="R80" s="1">
         <v>2</v>
@@ -7235,21 +7733,25 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W80" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="X80" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="Z80" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AB80" s="2" t="s">
-        <v>272</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:28">
@@ -7260,46 +7762,46 @@
         <v>80</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="1">
         <v>47</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="1">
         <v>44</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="1">
         <v>17</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="R81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S81" s="1">
         <v>1</v>
@@ -7307,21 +7809,25 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="W81" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="X81" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y81" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="Z81" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA81" s="2" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="AB81" s="2" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="1:28">
@@ -7332,64 +7838,72 @@
         <v>82</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="1">
         <v>13</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="1">
         <v>8</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="1">
         <v>6</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="R82" s="1">
+        <v>2</v>
+      </c>
+      <c r="S82" s="1">
+        <v>0</v>
+      </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W82" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="X82" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y82" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="Z82" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA82" s="2" t="s">
-        <v>278</v>
+        <v>64</v>
       </c>
       <c r="AB82" s="2" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" spans="1:28">
@@ -7400,64 +7914,72 @@
         <v>81</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="1">
         <v>25</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="1">
         <v>34</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="1">
         <v>4</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="R83" s="1"/>
-      <c r="S83" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="R83" s="1">
+        <v>3</v>
+      </c>
+      <c r="S83" s="1">
+        <v>2</v>
+      </c>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W83" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="X83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y83" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="Z83" s="2" t="s">
-        <v>39</v>
+        <v>315</v>
       </c>
       <c r="AA83" s="2" t="s">
-        <v>278</v>
+        <v>152</v>
       </c>
       <c r="AB83" s="2" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:28">
@@ -7468,64 +7990,72 @@
         <v>84</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="1">
         <v>41</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="1">
         <v>48</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="1">
         <v>3</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="R84" s="1"/>
-      <c r="S84" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="R84" s="1">
+        <v>2</v>
+      </c>
+      <c r="S84" s="1">
+        <v>1</v>
+      </c>
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W84" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="X84" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="Y84" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="Z84" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA84" s="2" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="AB84" s="2" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85" spans="1:28">
@@ -7536,64 +8066,72 @@
         <v>83</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="1">
         <v>30</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="1">
         <v>39</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="1">
         <v>13</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="R85" s="1"/>
-      <c r="S85" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="R85" s="1">
+        <v>3</v>
+      </c>
+      <c r="S85" s="1">
+        <v>0</v>
+      </c>
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
       <c r="V85" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W85" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="X85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y85" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="Z85" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA85" s="2" t="s">
-        <v>278</v>
+        <v>141</v>
       </c>
       <c r="AB85" s="2" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
     </row>
     <row r="86" spans="1:28">
@@ -7604,64 +8142,72 @@
         <v>85</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="1">
         <v>7</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="1">
         <v>38</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="1">
         <v>12</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="R86" s="1"/>
-      <c r="S86" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="R86" s="1">
+        <v>2</v>
+      </c>
+      <c r="S86" s="1">
+        <v>0</v>
+      </c>
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W86" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="X86" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="Y86" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="Z86" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA86" s="2" t="s">
-        <v>278</v>
+        <v>74</v>
       </c>
       <c r="AB86" s="2" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:28">
@@ -7672,64 +8218,68 @@
         <v>88</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="1">
         <v>43</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="1">
         <v>45</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="1">
         <v>2</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W87" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="X87" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="Y87" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="Z87" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA87" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB87" s="2" t="s">
-        <v>286</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:28">
@@ -7740,64 +8290,76 @@
         <v>86</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="1">
         <v>14</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="1">
         <v>26</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="1">
         <v>5</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="R88" s="1"/>
-      <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
-      <c r="U88" s="1"/>
+        <v>323</v>
+      </c>
+      <c r="R88" s="1">
+        <v>-1</v>
+      </c>
+      <c r="S88" s="1">
+        <v>1</v>
+      </c>
+      <c r="T88" s="1">
+        <v>4</v>
+      </c>
+      <c r="U88" s="1">
+        <v>4</v>
+      </c>
       <c r="V88" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W88" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="X88" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="Y88" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="Z88" s="2" t="s">
-        <v>39</v>
+        <v>300</v>
       </c>
       <c r="AA88" s="2" t="s">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="AB88" s="2" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" spans="1:28">
@@ -7808,64 +8370,72 @@
         <v>87</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="1">
         <v>37</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="1">
         <v>32</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="1">
         <v>8</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="R89" s="1"/>
-      <c r="S89" s="1"/>
+        <v>323</v>
+      </c>
+      <c r="R89" s="1">
+        <v>3</v>
+      </c>
+      <c r="S89" s="1">
+        <v>2</v>
+      </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W89" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>325</v>
+      </c>
       <c r="X89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y89" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="Y89" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="Z89" s="2" t="s">
-        <v>39</v>
+        <v>315</v>
       </c>
       <c r="AA89" s="2" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="AB89" s="2" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
     </row>
     <row r="90" spans="1:28">
@@ -7876,64 +8446,68 @@
         <v>90</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="1">
         <v>15</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="1">
         <v>33</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="1">
         <v>10</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W90" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="X90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y90" s="2" t="s">
+        <v>336</v>
+      </c>
       <c r="Z90" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA90" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB90" s="2" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
     </row>
     <row r="91" spans="1:28">
@@ -7944,64 +8518,68 @@
         <v>89</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="1">
         <v>5</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="1">
         <v>12</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="1">
         <v>7</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W91" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="X91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="Y91" s="2" t="s">
+        <v>336</v>
+      </c>
       <c r="Z91" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA91" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB91" s="2" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:28">
@@ -8012,64 +8590,68 @@
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="1">
         <v>9</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="1">
         <v>35</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="1">
         <v>1</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W92" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="X92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y92" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="Z92" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA92" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB92" s="2" t="s">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:28">
@@ -8080,16 +8662,28 @@
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D93" s="2"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
+      <c r="E93" s="1">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
+      <c r="I93" s="1">
+        <v>47</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="L93" s="2"/>
       <c r="M93" s="1">
         <v>14</v>
@@ -8101,31 +8695,35 @@
         <v>35</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W93" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="X93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y93" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="Z93" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA93" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB93" s="2" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:28">
@@ -8136,7 +8734,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="1"/>
@@ -8151,37 +8749,41 @@
         <v>2</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W94" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="X94" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y94" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="Z94" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA94" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB94" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:28">
@@ -8192,52 +8794,68 @@
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D95" s="2"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
+      <c r="E95" s="1">
+        <v>13</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="H95" s="2"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
+      <c r="I95" s="1">
+        <v>25</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="L95" s="2"/>
       <c r="M95" s="1">
         <v>6</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W95" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="X95" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y95" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="Y95" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="Z95" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA95" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB95" s="2" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
     </row>
     <row r="96" spans="1:28">
@@ -8248,7 +8866,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="1"/>
@@ -8263,37 +8881,41 @@
         <v>17</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W96" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>350</v>
+      </c>
       <c r="X96" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y96" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y96" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="Z96" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA96" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB96" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="97" spans="1:28">
@@ -8304,7 +8926,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="1"/>
@@ -8319,37 +8941,41 @@
         <v>12</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W97" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>350</v>
+      </c>
       <c r="X97" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y97" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="Z97" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA97" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB97" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:28">
@@ -8360,7 +8986,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="1"/>
@@ -8375,37 +9001,41 @@
         <v>9</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W98" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>354</v>
+      </c>
       <c r="X98" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="Y98" s="2" t="s">
+        <v>355</v>
+      </c>
       <c r="Z98" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA98" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB98" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="99" spans="1:28">
@@ -8416,7 +9046,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="1"/>
@@ -8431,37 +9061,41 @@
         <v>3</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W99" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>357</v>
+      </c>
       <c r="X99" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y99" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y99" s="2" t="s">
+        <v>356</v>
+      </c>
       <c r="Z99" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA99" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB99" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="100" spans="1:28">
@@ -8472,7 +9106,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="1"/>
@@ -8487,37 +9121,41 @@
         <v>5</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W100" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>359</v>
+      </c>
       <c r="X100" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y100" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="Z100" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA100" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB100" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="101" spans="1:28">
@@ -8528,7 +9166,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="1"/>
@@ -8543,37 +9181,41 @@
         <v>8</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W101" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>359</v>
+      </c>
       <c r="X101" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="Y101" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="Z101" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA101" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB101" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="102" spans="1:28">
@@ -8584,7 +9226,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="1"/>
@@ -8599,37 +9241,41 @@
         <v>2</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W102" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>362</v>
+      </c>
       <c r="X102" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y102" s="2" t="s">
+        <v>361</v>
+      </c>
       <c r="Z102" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA102" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB102" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103" spans="1:28">
@@ -8640,7 +9286,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="1"/>
@@ -8655,37 +9301,41 @@
         <v>17</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
       <c r="V103" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W103" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>364</v>
+      </c>
       <c r="X103" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y103" s="2" t="s">
+        <v>363</v>
+      </c>
       <c r="Z103" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA103" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB103" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="104" spans="1:28">
@@ -8696,7 +9346,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="1"/>
@@ -8711,37 +9361,41 @@
         <v>5</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W104" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>367</v>
+      </c>
       <c r="X104" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="Y104" s="2" t="s">
+        <v>366</v>
+      </c>
       <c r="Z104" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA104" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB104" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
     <row r="105" spans="1:28">
@@ -8752,7 +9406,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="1"/>
@@ -8767,37 +9421,41 @@
         <v>1</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="W105" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>370</v>
+      </c>
       <c r="X105" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y105" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y105" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="Z105" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA105" s="2" t="s">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="AB105" s="2" t="s">
-        <v>295</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/src/resultados_partidos.xlsx
+++ b/src/resultados_partidos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="379">
   <si>
     <t>id</t>
   </si>
@@ -988,112 +988,136 @@
     <t>03/07/2026</t>
   </si>
   <si>
+    <t>3 de julio</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>3/07/2026</t>
+  </si>
+  <si>
+    <t>Colombia vs Ghana</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>Australia vs Egipto</t>
+  </si>
+  <si>
+    <t>Argentina vs Cabo Verde</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>04/07/2026</t>
+  </si>
+  <si>
+    <t>4 de julio</t>
+  </si>
+  <si>
+    <t>4/07/2026</t>
+  </si>
+  <si>
+    <t>Paraguay vs Francia</t>
+  </si>
+  <si>
+    <t>Canadá vs Marruecos</t>
+  </si>
+  <si>
+    <t>05/07/2026</t>
+  </si>
+  <si>
+    <t>5 de julio</t>
+  </si>
+  <si>
+    <t>5/07/2026</t>
+  </si>
+  <si>
+    <t>Brasil vs Noruega</t>
+  </si>
+  <si>
+    <t>México vs Inglaterra</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>6 de julio</t>
+  </si>
+  <si>
+    <t>6/07/2026</t>
+  </si>
+  <si>
+    <t>Portugal vs España</t>
+  </si>
+  <si>
+    <t>Estados Unidos vs Bélgica</t>
+  </si>
+  <si>
+    <t>07/07/2026</t>
+  </si>
+  <si>
+    <t>in_progress</t>
+  </si>
+  <si>
+    <t>7 de julio</t>
+  </si>
+  <si>
+    <t>7/07/2026</t>
+  </si>
+  <si>
+    <t>En vivo</t>
+  </si>
+  <si>
+    <t>Argentina vs Egipto</t>
+  </si>
+  <si>
     <t>scheduled</t>
   </si>
   <si>
-    <t>3 de julio</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>3/07/2026</t>
-  </si>
-  <si>
     <t>Por jugar</t>
   </si>
   <si>
-    <t>Colombia vs Ghana</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>Australia vs Egipto</t>
-  </si>
-  <si>
-    <t>Argentina vs Cabo Verde</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>04/07/2026</t>
-  </si>
-  <si>
-    <t>4 de julio</t>
-  </si>
-  <si>
-    <t>4/07/2026</t>
-  </si>
-  <si>
-    <t>Paraguay vs Francia</t>
-  </si>
-  <si>
-    <t>Canadá vs Marruecos</t>
-  </si>
-  <si>
-    <t>05/07/2026</t>
-  </si>
-  <si>
-    <t>5 de julio</t>
-  </si>
-  <si>
-    <t>5/07/2026</t>
-  </si>
-  <si>
-    <t>Brasil vs Noruega</t>
-  </si>
-  <si>
-    <t>México vs Inglaterra</t>
-  </si>
-  <si>
-    <t>06/07/2026</t>
-  </si>
-  <si>
-    <t>6 de julio</t>
-  </si>
-  <si>
-    <t>6/07/2026</t>
+    <t>Suiza vs Colombia</t>
+  </si>
+  <si>
+    <t>QF</t>
+  </si>
+  <si>
+    <t>09/07/2026</t>
+  </si>
+  <si>
+    <t>9 de julio</t>
+  </si>
+  <si>
+    <t>9/07/2026</t>
+  </si>
+  <si>
+    <t>Francia vs Marruecos</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>10 de julio</t>
+  </si>
+  <si>
+    <t>España vs Bélgica</t>
+  </si>
+  <si>
+    <t>11/07/2026</t>
+  </si>
+  <si>
+    <t>11 de julio</t>
+  </si>
+  <si>
+    <t>Noruega vs Inglaterra</t>
   </si>
   <si>
     <t>Por definir vs Por definir</t>
-  </si>
-  <si>
-    <t>Estados Unidos vs Bélgica</t>
-  </si>
-  <si>
-    <t>07/07/2026</t>
-  </si>
-  <si>
-    <t>7 de julio</t>
-  </si>
-  <si>
-    <t>7/07/2026</t>
-  </si>
-  <si>
-    <t>QF</t>
-  </si>
-  <si>
-    <t>09/07/2026</t>
-  </si>
-  <si>
-    <t>9 de julio</t>
-  </si>
-  <si>
-    <t>9/07/2026</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>10 de julio</t>
-  </si>
-  <si>
-    <t>11/07/2026</t>
-  </si>
-  <si>
-    <t>11 de julio</t>
   </si>
   <si>
     <t>SF</t>
@@ -8256,30 +8280,34 @@
       <c r="Q87" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="R87" s="1"/>
-      <c r="S87" s="1"/>
+      <c r="R87" s="1">
+        <v>1</v>
+      </c>
+      <c r="S87" s="1">
+        <v>0</v>
+      </c>
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W87" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="W87" s="2" t="s">
+      <c r="X87" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="X87" s="2" t="s">
+      <c r="Y87" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="Y87" s="2" t="s">
+      <c r="Z87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA87" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB87" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="Z87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA87" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB87" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:28">
@@ -8329,13 +8357,13 @@
         <v>323</v>
       </c>
       <c r="R88" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S88" s="1">
         <v>1</v>
       </c>
       <c r="T88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U88" s="1">
         <v>4</v>
@@ -8344,13 +8372,13 @@
         <v>38</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z88" s="2" t="s">
         <v>300</v>
@@ -8359,7 +8387,7 @@
         <v>154</v>
       </c>
       <c r="AB88" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" spans="1:28">
@@ -8420,13 +8448,13 @@
         <v>38</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>88</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z89" s="2" t="s">
         <v>315</v>
@@ -8435,7 +8463,7 @@
         <v>185</v>
       </c>
       <c r="AB89" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:28">
@@ -8446,7 +8474,7 @@
         <v>90</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="1">
@@ -8482,32 +8510,36 @@
         <v>65</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
+        <v>332</v>
+      </c>
+      <c r="R90" s="1">
+        <v>0</v>
+      </c>
+      <c r="S90" s="1">
+        <v>1</v>
+      </c>
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="X90" s="2" t="s">
         <v>251</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="Z90" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA90" s="2" t="s">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="AB90" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:28">
@@ -8518,7 +8550,7 @@
         <v>89</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="1">
@@ -8554,32 +8586,36 @@
         <v>65</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
+        <v>332</v>
+      </c>
+      <c r="R91" s="1">
+        <v>0</v>
+      </c>
+      <c r="S91" s="1">
+        <v>3</v>
+      </c>
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="X91" s="2" t="s">
         <v>114</v>
       </c>
       <c r="Y91" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="Z91" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA91" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB91" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="Z91" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA91" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB91" s="2" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="92" spans="1:28">
@@ -8590,7 +8626,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="1">
@@ -8626,32 +8662,36 @@
         <v>65</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
+        <v>337</v>
+      </c>
+      <c r="R92" s="1">
+        <v>1</v>
+      </c>
+      <c r="S92" s="1">
+        <v>2</v>
+      </c>
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="X92" s="2" t="s">
         <v>123</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Z92" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA92" s="2" t="s">
-        <v>328</v>
+        <v>181</v>
       </c>
       <c r="AB92" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93" spans="1:28">
@@ -8662,7 +8702,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="1">
@@ -8698,32 +8738,36 @@
         <v>36</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R93" s="1"/>
-      <c r="S93" s="1"/>
+        <v>337</v>
+      </c>
+      <c r="R93" s="1">
+        <v>2</v>
+      </c>
+      <c r="S93" s="1">
+        <v>3</v>
+      </c>
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>239</v>
+        <v>70</v>
       </c>
       <c r="Y93" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="Z93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA93" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB93" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="Z93" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA93" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB93" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:28">
@@ -8734,16 +8778,28 @@
         <v>93</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D94" s="2"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
+      <c r="E94" s="1">
+        <v>41</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
+      <c r="I94" s="1">
+        <v>30</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="L94" s="2"/>
       <c r="M94" s="1">
         <v>2</v>
@@ -8758,32 +8814,36 @@
         <v>65</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="R94" s="1"/>
-      <c r="S94" s="1"/>
+        <v>342</v>
+      </c>
+      <c r="R94" s="1">
+        <v>0</v>
+      </c>
+      <c r="S94" s="1">
+        <v>1</v>
+      </c>
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Z94" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA94" s="2" t="s">
-        <v>328</v>
+        <v>141</v>
       </c>
       <c r="AB94" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="95" spans="1:28">
@@ -8794,7 +8854,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="1">
@@ -8830,32 +8890,36 @@
         <v>65</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="R95" s="1"/>
-      <c r="S95" s="1"/>
+        <v>342</v>
+      </c>
+      <c r="R95" s="1">
+        <v>1</v>
+      </c>
+      <c r="S95" s="1">
+        <v>4</v>
+      </c>
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="2" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="X95" s="2" t="s">
         <v>239</v>
       </c>
       <c r="Y95" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z95" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA95" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB95" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="Z95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA95" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AB95" s="2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="96" spans="1:28">
@@ -8866,16 +8930,28 @@
         <v>95</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D96" s="2"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
+      <c r="E96" s="1">
+        <v>37</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>186</v>
+      </c>
       <c r="H96" s="2"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
+      <c r="I96" s="1">
+        <v>26</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="L96" s="2"/>
       <c r="M96" s="1">
         <v>17</v>
@@ -8890,32 +8966,36 @@
         <v>65</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="R96" s="1"/>
-      <c r="S96" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="R96" s="1">
+        <v>0</v>
+      </c>
+      <c r="S96" s="1">
+        <v>1</v>
+      </c>
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="2" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X96" s="2" t="s">
         <v>149</v>
       </c>
       <c r="Y96" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA96" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="Z96" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA96" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="AB96" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:28">
@@ -8926,16 +9006,28 @@
         <v>96</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D97" s="2"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
+      <c r="E97" s="1">
+        <v>7</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="H97" s="2"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
+      <c r="I97" s="1">
+        <v>43</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="L97" s="2"/>
       <c r="M97" s="1">
         <v>12</v>
@@ -8950,32 +9042,32 @@
         <v>58</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X97" s="2" t="s">
         <v>123</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z97" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA97" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB97" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:28">
@@ -8986,16 +9078,28 @@
         <v>97</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D98" s="2"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
+      <c r="E98" s="1">
+        <v>33</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="H98" s="2"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
+      <c r="I98" s="1">
+        <v>12</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="L98" s="2"/>
       <c r="M98" s="1">
         <v>9</v>
@@ -9010,32 +9114,32 @@
         <v>65</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="X98" s="2" t="s">
         <v>123</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Z98" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA98" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB98" s="2" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:28">
@@ -9046,16 +9150,28 @@
         <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D99" s="2"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
+      <c r="E99" s="1">
+        <v>30</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
+      <c r="I99" s="1">
+        <v>25</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="L99" s="2"/>
       <c r="M99" s="1">
         <v>3</v>
@@ -9070,32 +9186,32 @@
         <v>65</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="X99" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Z99" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA99" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB99" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:28">
@@ -9106,16 +9222,28 @@
         <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D100" s="2"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
+      <c r="E100" s="1">
+        <v>35</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
+      <c r="I100" s="1">
+        <v>47</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="L100" s="2"/>
       <c r="M100" s="1">
         <v>5</v>
@@ -9130,32 +9258,32 @@
         <v>65</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="X100" s="2" t="s">
         <v>251</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Z100" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA100" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB100" s="2" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:28">
@@ -9166,7 +9294,7 @@
         <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="1"/>
@@ -9190,32 +9318,32 @@
         <v>65</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="X101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Z101" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA101" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB101" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:28">
@@ -9226,7 +9354,7 @@
         <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="1"/>
@@ -9250,32 +9378,32 @@
         <v>65</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z102" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA102" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB102" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:28">
@@ -9286,7 +9414,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="1"/>
@@ -9310,32 +9438,32 @@
         <v>65</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
       <c r="V103" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="X103" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA103" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB103" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:28">
@@ -9346,7 +9474,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="1"/>
@@ -9370,32 +9498,32 @@
         <v>65</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="X104" s="2" t="s">
         <v>251</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="Z104" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA104" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB104" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:28">
@@ -9406,7 +9534,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="1"/>
@@ -9430,32 +9558,32 @@
         <v>65</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="2" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="X105" s="2" t="s">
         <v>40</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Z105" s="2" t="s">
         <v>41</v>
       </c>
       <c r="AA105" s="2" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AB105" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
